--- a/Corte_3.xlsx
+++ b/Corte_3.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="899" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B87A3EB0-621F-4733-92B9-D488692010FE}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185550E2-598D-4B2E-AB82-D62DD59E97B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corte" sheetId="1" r:id="rId1"/>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="63">
   <si>
     <t>Asignatura</t>
   </si>
@@ -234,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,7 +523,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -536,16 +561,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -711,36 +726,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -756,16 +741,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -851,31 +826,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -891,51 +846,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="3"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -986,16 +901,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1335,7 +1240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" customWidth="1"/>
@@ -1347,7 +1252,7 @@
     <col min="24" max="24" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1364,7 +1269,7 @@
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
@@ -1381,7 +1286,7 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
@@ -1404,7 +1309,7 @@
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
@@ -1421,7 +1326,7 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
@@ -1471,7 +1376,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
@@ -1523,7 +1428,7 @@
       <c r="W7" s="11"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
@@ -1574,7 +1479,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>25</v>
       </c>
@@ -1625,7 +1530,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1676,7 +1581,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
@@ -1727,7 +1632,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
@@ -1779,7 +1684,7 @@
       </c>
       <c r="AA12" s="8"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>33</v>
       </c>
@@ -1830,7 +1735,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>35</v>
       </c>
@@ -1881,7 +1786,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>37</v>
       </c>
@@ -1932,7 +1837,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>39</v>
       </c>
@@ -1983,7 +1888,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>41</v>
       </c>
@@ -2034,7 +1939,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>43</v>
       </c>
@@ -2085,7 +1990,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>45</v>
       </c>
@@ -2136,7 +2041,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>47</v>
       </c>
@@ -2187,7 +2092,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>49</v>
       </c>
@@ -2238,7 +2143,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>1016912717</v>
       </c>
@@ -2339,74 +2244,44 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:L21">
-    <cfRule type="expression" dxfId="47" priority="14">
+  <conditionalFormatting sqref="E8:E22">
+    <cfRule type="expression" dxfId="37" priority="1">
+      <formula>E8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="2">
+      <formula>E8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:L22">
+    <cfRule type="expression" dxfId="35" priority="5">
+      <formula>G8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>G8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:L21">
-    <cfRule type="expression" dxfId="46" priority="13">
-      <formula>G8&gt;=3</formula>
+  <conditionalFormatting sqref="N8:N22">
+    <cfRule type="expression" dxfId="33" priority="11">
+      <formula>N8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N22">
-    <cfRule type="expression" dxfId="45" priority="12">
+    <cfRule type="expression" dxfId="32" priority="12">
       <formula>N8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N22">
-    <cfRule type="expression" dxfId="44" priority="11">
-      <formula>N8&gt;=3</formula>
+  <conditionalFormatting sqref="P8:T22">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="30" priority="4">
+      <formula>LEN(TRIM(P8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V8:V22">
-    <cfRule type="expression" dxfId="43" priority="10">
-      <formula>V8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V22">
-    <cfRule type="expression" dxfId="42" priority="9">
+    <cfRule type="expression" dxfId="29" priority="9">
       <formula>V8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:T21">
-    <cfRule type="containsBlanks" dxfId="41" priority="8">
-      <formula>LEN(TRIM(P8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:T21">
-    <cfRule type="cellIs" dxfId="40" priority="7" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:L22">
-    <cfRule type="expression" dxfId="39" priority="6">
-      <formula>G22&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:L22">
-    <cfRule type="expression" dxfId="38" priority="5">
-      <formula>G22&gt;=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P22:T22">
-    <cfRule type="containsBlanks" dxfId="37" priority="4">
-      <formula>LEN(TRIM(P22))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P22:T22">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E22">
-    <cfRule type="expression" dxfId="35" priority="2">
-      <formula>E8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E22">
-    <cfRule type="expression" dxfId="34" priority="1">
-      <formula>E8&gt;=3</formula>
+    <cfRule type="expression" dxfId="28" priority="10">
+      <formula>V8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2416,7 +2291,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865D47EF-51ED-406F-A091-BAA11C63147F}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -2430,7 +2305,7 @@
     <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2444,7 +2319,7 @@
       <c r="G1" s="23"/>
       <c r="H1" s="23"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
@@ -2458,7 +2333,7 @@
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
@@ -2472,7 +2347,7 @@
       <c r="G3" s="23"/>
       <c r="H3" s="23"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
@@ -2486,7 +2361,7 @@
       <c r="G4" s="38"/>
       <c r="H4" s="38"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
@@ -2531,7 +2406,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
@@ -2560,7 +2435,7 @@
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
@@ -2573,7 +2448,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="1">
-        <f>E8*0.1</f>
+        <f t="shared" ref="F8:F22" si="0">E8*0.1</f>
         <v>0.5</v>
       </c>
       <c r="G8" s="1">
@@ -2590,7 +2465,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" s="6">
-        <f>J8*0.5</f>
+        <f t="shared" ref="K8:K22" si="1">J8*0.5</f>
         <v>1.7</v>
       </c>
       <c r="L8" s="6"/>
@@ -2599,15 +2474,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="6">
-        <f>F8+I8+K8</f>
+        <f t="shared" ref="N8:N22" si="2">F8+I8+K8</f>
         <v>4.0600000000000005</v>
       </c>
       <c r="O8" s="6">
-        <f>INT(N8*10)/10+IF(MOD(N8*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" ref="O8:O22" si="3">INT(N8*10)/10+IF(MOD(N8*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="P8" s="1" t="str">
-        <f>IF(N8&lt;3,3-N8,"No aplica")</f>
+        <f t="shared" ref="P8:P22" si="4">IF(N8&lt;3,3-N8,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q8" s="1">
@@ -2615,7 +2490,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>25</v>
       </c>
@@ -2628,7 +2503,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="1">
-        <f>E9*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="G9" s="1">
@@ -2638,14 +2513,14 @@
         <v>4.5</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" ref="I9:I22" si="0">(G9*0.3+H9*0.7)*0.4</f>
+        <f t="shared" ref="I9:I21" si="5">(G9*0.3+H9*0.7)*0.4</f>
         <v>1.8600000000000003</v>
       </c>
       <c r="J9" s="1">
         <v>2.9</v>
       </c>
       <c r="K9" s="6">
-        <f>J9*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.45</v>
       </c>
       <c r="L9" s="6">
@@ -2656,23 +2531,23 @@
         <v>0.15</v>
       </c>
       <c r="N9" s="6">
-        <f>F9+I9+K9</f>
+        <f t="shared" si="2"/>
         <v>3.8100000000000005</v>
       </c>
       <c r="O9" s="6">
-        <f>INT(N9*10)/10+IF(MOD(N9*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.8</v>
       </c>
       <c r="P9" s="1" t="str">
-        <f>IF(N9&lt;3,3-N9,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" ref="Q9:Q22" si="1">O9+M9</f>
+        <f t="shared" ref="Q9:Q22" si="6">O9+M9</f>
         <v>3.9499999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2685,7 +2560,7 @@
         <v>3.5</v>
       </c>
       <c r="F10" s="1">
-        <f>E10*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="G10" s="1">
@@ -2695,39 +2570,39 @@
         <v>4.2</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.7759999999999998</v>
       </c>
       <c r="J10" s="1">
         <v>3.25</v>
       </c>
       <c r="K10" s="6">
-        <f>J10*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.625</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6">
-        <f t="shared" ref="M10:M22" si="2">L10/10</f>
+        <f t="shared" ref="M10:M22" si="7">L10/10</f>
         <v>0</v>
       </c>
       <c r="N10" s="6">
-        <f>F10+I10+K10</f>
+        <f t="shared" si="2"/>
         <v>3.7509999999999999</v>
       </c>
       <c r="O10" s="6">
-        <f>INT(N10*10)/10+IF(MOD(N10*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="P10" s="1" t="str">
-        <f>IF(N10&lt;3,3-N10,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8000000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
@@ -2740,7 +2615,7 @@
         <v>3.1</v>
       </c>
       <c r="F11" s="1">
-        <f>E11*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.31000000000000005</v>
       </c>
       <c r="G11" s="1">
@@ -2750,41 +2625,41 @@
         <v>4.2</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.7759999999999998</v>
       </c>
       <c r="J11" s="1">
         <v>4.4000000000000004</v>
       </c>
       <c r="K11" s="6">
-        <f>J11*0.5</f>
+        <f t="shared" si="1"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="L11" s="6">
         <v>1.5</v>
       </c>
       <c r="M11" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N11" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N11" s="6">
-        <f>F11+I11+K11</f>
         <v>4.2859999999999996</v>
       </c>
       <c r="O11" s="6">
-        <f>INT(N11*10)/10+IF(MOD(N11*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.3</v>
       </c>
       <c r="P11" s="1" t="str">
-        <f>IF(N11&lt;3,3-N11,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.45</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
@@ -2797,7 +2672,7 @@
         <v>3.4</v>
       </c>
       <c r="F12" s="1">
-        <f>E12*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="G12" s="1">
@@ -2807,41 +2682,41 @@
         <v>4.8</v>
       </c>
       <c r="I12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.944</v>
       </c>
       <c r="J12" s="1">
         <v>3.7</v>
       </c>
       <c r="K12" s="6">
-        <f>J12*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.85</v>
       </c>
       <c r="L12" s="6">
         <v>1.5</v>
       </c>
       <c r="M12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N12" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N12" s="6">
-        <f>F12+I12+K12</f>
         <v>4.1340000000000003</v>
       </c>
       <c r="O12" s="6">
-        <f>INT(N12*10)/10+IF(MOD(N12*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="P12" s="1" t="str">
-        <f>IF(N12&lt;3,3-N12,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>33</v>
       </c>
@@ -2854,7 +2729,7 @@
         <v>3.5</v>
       </c>
       <c r="F13" s="1">
-        <f>E13*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="G13" s="1">
@@ -2864,41 +2739,41 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.8320000000000001</v>
       </c>
       <c r="J13" s="1">
         <v>3.98</v>
       </c>
       <c r="K13" s="6">
-        <f>J13*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.99</v>
       </c>
       <c r="L13" s="6">
         <v>1.5</v>
       </c>
       <c r="M13" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N13" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N13" s="6">
-        <f>F13+I13+K13</f>
         <v>4.1719999999999997</v>
       </c>
       <c r="O13" s="6">
-        <f>INT(N13*10)/10+IF(MOD(N13*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="P13" s="1" t="str">
-        <f>IF(N13&lt;3,3-N13,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>1016912717</v>
       </c>
@@ -2911,7 +2786,7 @@
         <v>2.8</v>
       </c>
       <c r="F14" s="1">
-        <f>E14*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.27999999999999997</v>
       </c>
       <c r="G14" s="1">
@@ -2921,41 +2796,41 @@
         <v>5</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J14" s="1">
         <v>4.7549999999999999</v>
       </c>
       <c r="K14" s="6">
-        <f>J14*0.5</f>
+        <f t="shared" si="1"/>
         <v>2.3774999999999999</v>
       </c>
       <c r="L14" s="6">
         <v>1.5</v>
       </c>
       <c r="M14" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N14" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N14" s="6">
-        <f>F14+I14+K14</f>
         <v>4.6574999999999998</v>
       </c>
       <c r="O14" s="6">
-        <f>INT(N14*10)/10+IF(MOD(N14*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.6999999999999993</v>
       </c>
       <c r="P14" s="1" t="str">
-        <f>IF(N14&lt;3,3-N14,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>35</v>
       </c>
@@ -2968,7 +2843,7 @@
         <v>3.7</v>
       </c>
       <c r="F15" s="1">
-        <f>E15*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.37000000000000005</v>
       </c>
       <c r="G15" s="1">
@@ -2978,41 +2853,41 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.8320000000000001</v>
       </c>
       <c r="J15" s="1">
         <v>3.65</v>
       </c>
       <c r="K15" s="6">
-        <f>J15*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.825</v>
       </c>
       <c r="L15" s="6">
         <v>1.5</v>
       </c>
       <c r="M15" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N15" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N15" s="6">
-        <f>F15+I15+K15</f>
         <v>4.0270000000000001</v>
       </c>
       <c r="O15" s="6">
-        <f>INT(N15*10)/10+IF(MOD(N15*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P15" s="1" t="str">
-        <f>IF(N15&lt;3,3-N15,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>37</v>
       </c>
@@ -3025,7 +2900,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="1">
-        <f>E16*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="G16" s="1">
@@ -3035,41 +2910,41 @@
         <v>4</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.72</v>
       </c>
       <c r="J16" s="1">
         <v>2.2999999999999998</v>
       </c>
       <c r="K16" s="6">
-        <f>J16*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.1499999999999999</v>
       </c>
       <c r="L16" s="6">
         <v>2.5</v>
       </c>
       <c r="M16" s="6">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="N16" s="6">
         <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="N16" s="6">
-        <f>F16+I16+K16</f>
         <v>3.07</v>
       </c>
       <c r="O16" s="6">
-        <f>INT(N16*10)/10+IF(MOD(N16*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.1</v>
       </c>
       <c r="P16" s="1" t="str">
-        <f>IF(N16&lt;3,3-N16,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.35</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>39</v>
       </c>
@@ -3082,7 +2957,7 @@
         <v>3.4</v>
       </c>
       <c r="F17" s="1">
-        <f>E17*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="G17" s="1">
@@ -3092,41 +2967,41 @@
         <v>4.8</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.944</v>
       </c>
       <c r="J17" s="1">
         <v>4.8499999999999996</v>
       </c>
       <c r="K17" s="6">
-        <f>J17*0.5</f>
+        <f t="shared" si="1"/>
         <v>2.4249999999999998</v>
       </c>
       <c r="L17" s="6">
         <v>1.5</v>
       </c>
       <c r="M17" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N17" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N17" s="6">
-        <f>F17+I17+K17</f>
         <v>4.7089999999999996</v>
       </c>
       <c r="O17" s="6">
-        <f>INT(N17*10)/10+IF(MOD(N17*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.7</v>
       </c>
       <c r="P17" s="1" t="str">
-        <f>IF(N17&lt;3,3-N17,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.8500000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>41</v>
       </c>
@@ -3139,7 +3014,7 @@
         <v>3.2</v>
       </c>
       <c r="F18" s="1">
-        <f>E18*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.32000000000000006</v>
       </c>
       <c r="G18" s="1">
@@ -3149,41 +3024,41 @@
         <v>4.5</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.8600000000000003</v>
       </c>
       <c r="J18" s="1">
         <v>4.5999999999999996</v>
       </c>
       <c r="K18" s="6">
-        <f>J18*0.5</f>
+        <f t="shared" si="1"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="L18" s="6">
         <v>1.5</v>
       </c>
       <c r="M18" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N18" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N18" s="6">
-        <f>F18+I18+K18</f>
         <v>4.4800000000000004</v>
       </c>
       <c r="O18" s="6">
-        <f>INT(N18*10)/10+IF(MOD(N18*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="P18" s="1" t="str">
-        <f>IF(N18&lt;3,3-N18,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>43</v>
       </c>
@@ -3196,7 +3071,7 @@
         <v>1.8</v>
       </c>
       <c r="F19" s="1">
-        <f>E19*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="G19" s="1">
@@ -3206,39 +3081,39 @@
         <v>4.8</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.944</v>
       </c>
       <c r="J19" s="1">
         <v>2.4500000000000002</v>
       </c>
       <c r="K19" s="6">
-        <f>J19*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.2250000000000001</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="6">
-        <f>F19+I19+K19</f>
         <v>3.3490000000000002</v>
       </c>
       <c r="O19" s="6">
-        <f>INT(N19*10)/10+IF(MOD(N19*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.3</v>
       </c>
       <c r="P19" s="1" t="str">
-        <f>IF(N19&lt;3,3-N19,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>45</v>
       </c>
@@ -3251,7 +3126,7 @@
         <v>2.6</v>
       </c>
       <c r="F20" s="1">
-        <f>E20*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.26</v>
       </c>
       <c r="G20" s="1">
@@ -3261,41 +3136,41 @@
         <v>5</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J20" s="1">
         <v>3.85</v>
       </c>
       <c r="K20" s="6">
-        <f>J20*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.925</v>
       </c>
       <c r="L20" s="6">
         <v>1.5</v>
       </c>
       <c r="M20" s="6">
+        <f t="shared" si="7"/>
+        <v>0.15</v>
+      </c>
+      <c r="N20" s="6">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="N20" s="6">
-        <f>F20+I20+K20</f>
         <v>4.1849999999999996</v>
       </c>
       <c r="O20" s="6">
-        <f>INT(N20*10)/10+IF(MOD(N20*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="P20" s="1" t="str">
-        <f>IF(N20&lt;3,3-N20,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -3308,7 +3183,7 @@
         <v>3.9</v>
       </c>
       <c r="F21" s="1">
-        <f>E21*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.39</v>
       </c>
       <c r="G21" s="1">
@@ -3318,39 +3193,39 @@
         <v>4.8</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1.944</v>
       </c>
       <c r="J21" s="1">
         <v>3</v>
       </c>
       <c r="K21" s="6">
-        <f>J21*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="6">
-        <f>F21+I21+K21</f>
         <v>3.8340000000000001</v>
       </c>
       <c r="O21" s="6">
-        <f>INT(N21*10)/10+IF(MOD(N21*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.8</v>
       </c>
       <c r="P21" s="1" t="str">
-        <f>IF(N21&lt;3,3-N21,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>49</v>
       </c>
@@ -3363,7 +3238,7 @@
         <v>2.5</v>
       </c>
       <c r="F22" s="1">
-        <f>E22*0.1</f>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="G22" s="1">
@@ -3380,28 +3255,28 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="K22" s="6">
-        <f>J22*0.5</f>
+        <f t="shared" si="1"/>
         <v>2.1749999999999998</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="6">
-        <f>F22+I22+K22</f>
         <v>4.2009999999999996</v>
       </c>
       <c r="O22" s="6">
-        <f>INT(N22*10)/10+IF(MOD(N22*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.2</v>
       </c>
       <c r="P22" s="1" t="str">
-        <f>IF(N22&lt;3,3-N22,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
       <c r="Q22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.2</v>
       </c>
     </row>
@@ -3457,62 +3332,44 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:D22"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:H21">
-    <cfRule type="expression" dxfId="33" priority="16">
+  <conditionalFormatting sqref="E8:E22">
+    <cfRule type="expression" dxfId="27" priority="3">
+      <formula>E8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="4">
+      <formula>E8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:H22">
+    <cfRule type="expression" dxfId="25" priority="7">
+      <formula>G8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="8">
       <formula>G8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:H21">
-    <cfRule type="expression" dxfId="32" priority="15">
-      <formula>G8&gt;=3</formula>
+  <conditionalFormatting sqref="J8:J22">
+    <cfRule type="expression" dxfId="23" priority="13">
+      <formula>J8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J22">
-    <cfRule type="expression" dxfId="31" priority="14">
+    <cfRule type="expression" dxfId="22" priority="14">
       <formula>J8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J22">
-    <cfRule type="expression" dxfId="30" priority="13">
-      <formula>J8&gt;=3</formula>
+  <conditionalFormatting sqref="L8:L22">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="20" priority="2">
+      <formula>LEN(TRIM(L8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N22">
-    <cfRule type="expression" dxfId="29" priority="12">
-      <formula>N8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N22">
-    <cfRule type="expression" dxfId="28" priority="11">
+    <cfRule type="expression" dxfId="19" priority="11">
       <formula>N8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:H22">
-    <cfRule type="expression" dxfId="27" priority="8">
-      <formula>G22&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G22:H22">
-    <cfRule type="expression" dxfId="26" priority="7">
-      <formula>G22&gt;=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E22">
-    <cfRule type="expression" dxfId="25" priority="4">
-      <formula>E8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E22">
-    <cfRule type="expression" dxfId="24" priority="3">
-      <formula>E8&gt;=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L8:L22">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="22" priority="2">
-      <formula>LEN(TRIM(L8))=0</formula>
+    <cfRule type="expression" dxfId="18" priority="12">
+      <formula>N8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3522,7 +3379,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA64364-85F1-4B4C-B1BB-0179859BFB61}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.5703125" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -3533,7 +3390,7 @@
     <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -3548,7 +3405,7 @@
       <c r="H1" s="23"/>
       <c r="I1" s="23"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
@@ -3563,7 +3420,7 @@
       <c r="H2" s="36"/>
       <c r="I2" s="36"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
@@ -3578,7 +3435,7 @@
       <c r="H3" s="23"/>
       <c r="I3" s="23"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
@@ -3593,7 +3450,7 @@
       <c r="H4" s="38"/>
       <c r="I4" s="38"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
@@ -3632,7 +3489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
@@ -3657,7 +3514,7 @@
       <c r="N7" s="11"/>
       <c r="O7" s="9"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
@@ -3683,30 +3540,30 @@
         <v>4.5</v>
       </c>
       <c r="J8" s="5">
-        <f>AVERAGE(H8:I8)*0.4</f>
+        <f t="shared" ref="J8:J22" si="0">AVERAGE(H8:I8)*0.4</f>
         <v>1.6600000000000001</v>
       </c>
       <c r="K8" s="1">
         <v>3.8</v>
       </c>
       <c r="L8" s="6">
-        <f>K8*0.5</f>
+        <f t="shared" ref="L8:L22" si="1">K8*0.5</f>
         <v>1.9</v>
       </c>
       <c r="M8" s="6">
-        <f>G8+J8+L8</f>
+        <f t="shared" ref="M8:M22" si="2">G8+J8+L8</f>
         <v>3.97</v>
       </c>
       <c r="N8" s="6">
-        <f>INT(M8*10)/10+IF(MOD(M8*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" ref="N8:N22" si="3">INT(M8*10)/10+IF(MOD(M8*10,1)&gt;=0.5,0.1,0)</f>
         <v>4</v>
       </c>
       <c r="O8" s="1" t="str">
-        <f>IF(M8&lt;3,3-M8,"No aplica")</f>
+        <f t="shared" ref="O8:O22" si="4">IF(M8&lt;3,3-M8,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>25</v>
       </c>
@@ -3722,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" ref="G9:G22" si="0">(E9+F9)*0.1</f>
+        <f t="shared" ref="G9:G22" si="5">(E9+F9)*0.1</f>
         <v>0.34</v>
       </c>
       <c r="H9" s="1">
@@ -3732,30 +3589,30 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="J9" s="5">
-        <f>AVERAGE(H9:I9)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.4800000000000002</v>
       </c>
       <c r="K9" s="1">
         <v>2.25</v>
       </c>
       <c r="L9" s="6">
-        <f>K9*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.125</v>
       </c>
       <c r="M9" s="6">
-        <f>G9+J9+L9</f>
+        <f t="shared" si="2"/>
         <v>2.9450000000000003</v>
       </c>
       <c r="N9" s="6">
-        <f>INT(M9*10)/10+IF(MOD(M9*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>2.9</v>
       </c>
       <c r="O9" s="1">
-        <f>IF(M9&lt;3,3-M9,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>5.4999999999999716E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -3771,7 +3628,7 @@
         <v>0.2</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H10" s="1">
@@ -3781,30 +3638,30 @@
         <v>4.8</v>
       </c>
       <c r="J10" s="5">
-        <f>AVERAGE(H10:I10)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.8600000000000003</v>
       </c>
       <c r="K10" s="1">
         <v>3.5</v>
       </c>
       <c r="L10" s="6">
-        <f>K10*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
       <c r="M10" s="6">
-        <f>G10+J10+L10</f>
+        <f t="shared" si="2"/>
         <v>3.7600000000000002</v>
       </c>
       <c r="N10" s="6">
-        <f>INT(M10*10)/10+IF(MOD(M10*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="O10" s="1" t="str">
-        <f>IF(M10&lt;3,3-M10,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
@@ -3820,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.26</v>
       </c>
       <c r="H11" s="1">
@@ -3830,30 +3687,30 @@
         <v>4.8</v>
       </c>
       <c r="J11" s="5">
-        <f>AVERAGE(H11:I11)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.8600000000000003</v>
       </c>
       <c r="K11" s="1">
         <v>3.6</v>
       </c>
       <c r="L11" s="6">
-        <f>K11*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
       <c r="M11" s="6">
-        <f>G11+J11+L11</f>
+        <f t="shared" si="2"/>
         <v>3.92</v>
       </c>
       <c r="N11" s="6">
-        <f>INT(M11*10)/10+IF(MOD(M11*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.9</v>
       </c>
       <c r="O11" s="1" t="str">
-        <f>IF(M11&lt;3,3-M11,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
@@ -3869,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.38</v>
       </c>
       <c r="H12" s="1">
@@ -3879,30 +3736,30 @@
         <v>4.8</v>
       </c>
       <c r="J12" s="5">
-        <f>AVERAGE(H12:I12)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.8600000000000003</v>
       </c>
       <c r="K12" s="1">
         <v>3.6</v>
       </c>
       <c r="L12" s="6">
-        <f>K12*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
       <c r="M12" s="6">
-        <f>G12+J12+L12</f>
+        <f t="shared" si="2"/>
         <v>4.04</v>
       </c>
       <c r="N12" s="6">
-        <f>INT(M12*10)/10+IF(MOD(M12*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="O12" s="1" t="str">
-        <f>IF(M12&lt;3,3-M12,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>33</v>
       </c>
@@ -3918,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.4</v>
       </c>
       <c r="H13" s="1">
@@ -3928,30 +3785,30 @@
         <v>5</v>
       </c>
       <c r="J13" s="5">
-        <f>AVERAGE(H13:I13)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.94</v>
       </c>
       <c r="K13" s="1">
         <v>3</v>
       </c>
       <c r="L13" s="6">
-        <f>K13*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="M13" s="6">
-        <f>G13+J13+L13</f>
+        <f t="shared" si="2"/>
         <v>3.84</v>
       </c>
       <c r="N13" s="6">
-        <f>INT(M13*10)/10+IF(MOD(M13*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.8</v>
       </c>
       <c r="O13" s="1" t="str">
-        <f>IF(M13&lt;3,3-M13,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>1016912717</v>
       </c>
@@ -3967,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
       <c r="H14" s="1">
@@ -3977,30 +3834,30 @@
         <v>5</v>
       </c>
       <c r="J14" s="5">
-        <f>AVERAGE(H14:I14)*0.4</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="K14" s="1">
         <v>4.4000000000000004</v>
       </c>
       <c r="L14" s="6">
-        <f>K14*0.5</f>
+        <f t="shared" si="1"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="M14" s="6">
-        <f>G14+J14+L14</f>
+        <f t="shared" si="2"/>
         <v>4.7</v>
       </c>
       <c r="N14" s="6">
-        <f>INT(M14*10)/10+IF(MOD(M14*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.7</v>
       </c>
       <c r="O14" s="1" t="str">
-        <f>IF(M14&lt;3,3-M14,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>35</v>
       </c>
@@ -4016,7 +3873,7 @@
         <v>0.2</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.34000000000000008</v>
       </c>
       <c r="H15" s="1">
@@ -4026,30 +3883,30 @@
         <v>5</v>
       </c>
       <c r="J15" s="5">
-        <f>AVERAGE(H15:I15)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.9600000000000002</v>
       </c>
       <c r="K15" s="1">
         <v>3.6</v>
       </c>
       <c r="L15" s="6">
-        <f>K15*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
       <c r="M15" s="6">
-        <f>G15+J15+L15</f>
+        <f t="shared" si="2"/>
         <v>4.1000000000000005</v>
       </c>
       <c r="N15" s="6">
-        <f>INT(M15*10)/10+IF(MOD(M15*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="O15" s="1" t="str">
-        <f>IF(M15&lt;3,3-M15,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>37</v>
       </c>
@@ -4065,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="H16" s="1">
@@ -4075,30 +3932,30 @@
         <v>4.8</v>
       </c>
       <c r="J16" s="5">
-        <f>AVERAGE(H16:I16)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.88</v>
       </c>
       <c r="K16" s="1">
         <v>3.5</v>
       </c>
       <c r="L16" s="6">
-        <f>K16*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
       <c r="M16" s="6">
-        <f>G16+J16+L16</f>
+        <f t="shared" si="2"/>
         <v>3.92</v>
       </c>
       <c r="N16" s="6">
-        <f>INT(M16*10)/10+IF(MOD(M16*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.9</v>
       </c>
       <c r="O16" s="1" t="str">
-        <f>IF(M16&lt;3,3-M16,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>39</v>
       </c>
@@ -4114,7 +3971,7 @@
         <v>0.2</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="H17" s="1">
@@ -4124,30 +3981,30 @@
         <v>4.7</v>
       </c>
       <c r="J17" s="5">
-        <f>AVERAGE(H17:I17)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.8600000000000003</v>
       </c>
       <c r="K17" s="1">
         <v>3</v>
       </c>
       <c r="L17" s="6">
-        <f>K17*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="M17" s="6">
-        <f>G17+J17+L17</f>
+        <f t="shared" si="2"/>
         <v>3.5900000000000003</v>
       </c>
       <c r="N17" s="6">
-        <f>INT(M17*10)/10+IF(MOD(M17*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
       <c r="O17" s="1" t="str">
-        <f>IF(M17&lt;3,3-M17,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>41</v>
       </c>
@@ -4163,7 +4020,7 @@
         <v>0.2</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.49000000000000005</v>
       </c>
       <c r="H18" s="1">
@@ -4173,30 +4030,30 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="J18" s="5">
-        <f>AVERAGE(H18:I18)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.9800000000000002</v>
       </c>
       <c r="K18" s="1">
         <v>3.4</v>
       </c>
       <c r="L18" s="6">
-        <f>K18*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
       <c r="M18" s="6">
-        <f>G18+J18+L18</f>
+        <f t="shared" si="2"/>
         <v>4.17</v>
       </c>
       <c r="N18" s="6">
-        <f>INT(M18*10)/10+IF(MOD(M18*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="O18" s="1" t="str">
-        <f>IF(M18&lt;3,3-M18,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>43</v>
       </c>
@@ -4212,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
       <c r="H19" s="1">
@@ -4222,30 +4079,30 @@
         <v>5</v>
       </c>
       <c r="J19" s="5">
-        <f>AVERAGE(H19:I19)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.9600000000000002</v>
       </c>
       <c r="K19" s="1">
         <v>1.2</v>
       </c>
       <c r="L19" s="6">
-        <f>K19*0.5</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="M19" s="6">
-        <f>G19+J19+L19</f>
+        <f t="shared" si="2"/>
         <v>2.6100000000000003</v>
       </c>
       <c r="N19" s="6">
-        <f>INT(M19*10)/10+IF(MOD(M19*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
       <c r="O19" s="1">
-        <f>IF(M19&lt;3,3-M19,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>0.38999999999999968</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>45</v>
       </c>
@@ -4261,7 +4118,7 @@
         <v>0.2</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="H20" s="1">
@@ -4271,30 +4128,30 @@
         <v>4.95</v>
       </c>
       <c r="J20" s="5">
-        <f>AVERAGE(H20:I20)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="K20" s="1">
         <v>1.8</v>
       </c>
       <c r="L20" s="6">
-        <f>K20*0.5</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="M20" s="6">
-        <f>G20+J20+L20</f>
+        <f t="shared" si="2"/>
         <v>3.19</v>
       </c>
       <c r="N20" s="6">
-        <f>INT(M20*10)/10+IF(MOD(M20*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.2</v>
       </c>
       <c r="O20" s="1" t="str">
-        <f>IF(M20&lt;3,3-M20,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -4310,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="H21" s="1">
@@ -4320,30 +4177,30 @@
         <v>4.7</v>
       </c>
       <c r="J21" s="5">
-        <f>AVERAGE(H21:I21)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.74</v>
       </c>
       <c r="K21" s="1">
         <v>2.9</v>
       </c>
       <c r="L21" s="6">
-        <f>K21*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.45</v>
       </c>
       <c r="M21" s="6">
-        <f>G21+J21+L21</f>
+        <f t="shared" si="2"/>
         <v>3.54</v>
       </c>
       <c r="N21" s="6">
-        <f>INT(M21*10)/10+IF(MOD(M21*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
       <c r="O21" s="1" t="str">
-        <f>IF(M21&lt;3,3-M21,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>49</v>
       </c>
@@ -4359,7 +4216,7 @@
         <v>0.2</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="H22" s="1">
@@ -4369,26 +4226,26 @@
         <v>4</v>
       </c>
       <c r="J22" s="5">
-        <f>AVERAGE(H22:I22)*0.4</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="K22" s="1">
         <v>3.2</v>
       </c>
       <c r="L22" s="6">
-        <f>K22*0.5</f>
+        <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
       <c r="M22" s="6">
-        <f>G22+J22+L22</f>
+        <f t="shared" si="2"/>
         <v>3.68</v>
       </c>
       <c r="N22" s="6">
-        <f>INT(M22*10)/10+IF(MOD(M22*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="3"/>
         <v>3.7</v>
       </c>
       <c r="O22" s="1" t="str">
-        <f>IF(M22&lt;3,3-M22,"No aplica")</f>
+        <f t="shared" si="4"/>
         <v>No aplica</v>
       </c>
     </row>
@@ -4444,54 +4301,36 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:I3"/>
   </mergeCells>
-  <conditionalFormatting sqref="H8:I21">
-    <cfRule type="expression" dxfId="21" priority="12">
+  <conditionalFormatting sqref="E8:F22">
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>E8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="4">
+      <formula>E8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:I22">
+    <cfRule type="expression" dxfId="15" priority="5">
+      <formula>H8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="6">
       <formula>H8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:I21">
-    <cfRule type="expression" dxfId="20" priority="11">
-      <formula>H8&gt;=3</formula>
+  <conditionalFormatting sqref="K8:K22">
+    <cfRule type="expression" dxfId="13" priority="9">
+      <formula>K8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K22">
-    <cfRule type="expression" dxfId="19" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>K8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K22">
-    <cfRule type="expression" dxfId="18" priority="9">
-      <formula>K8&gt;=3</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="M8:M22">
-    <cfRule type="expression" dxfId="17" priority="8">
-      <formula>M8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M8:M22">
-    <cfRule type="expression" dxfId="16" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>M8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22">
-    <cfRule type="expression" dxfId="15" priority="6">
-      <formula>H22&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22">
-    <cfRule type="expression" dxfId="14" priority="5">
-      <formula>H22&gt;=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:F22">
-    <cfRule type="expression" dxfId="13" priority="4">
-      <formula>E8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:F22">
-    <cfRule type="expression" dxfId="12" priority="3">
-      <formula>E8&gt;=3</formula>
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>M8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4500,8 +4339,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D02CB94-BE69-462D-965B-A4EABD13502C}">
-  <dimension ref="A1:R22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
@@ -4512,10 +4351,9 @@
     <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -4530,7 +4368,7 @@
       <c r="H1" s="23"/>
       <c r="I1" s="23"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
@@ -4545,7 +4383,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="23"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
@@ -4560,7 +4398,7 @@
       <c r="H3" s="31"/>
       <c r="I3" s="31"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
@@ -4575,7 +4413,7 @@
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
@@ -4617,11 +4455,8 @@
       <c r="Q6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
@@ -4638,10 +4473,10 @@
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
@@ -4653,9 +4488,8 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-    </row>
-    <row r="8" spans="1:18">
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>1028943852</v>
       </c>
@@ -4668,54 +4502,50 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="G8" s="1">
         <f>(E8*0.35+F8*0.65)*0.1</f>
-        <v>0.16500000000000001</v>
+        <v>0.26900000000000007</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="I8" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J8" s="5">
-        <f>AVERAGE(H8:I8)*0.4</f>
-        <v>0.60000000000000009</v>
+        <f>(AVERAGE(H8:I8)+N8)*0.4</f>
+        <v>2.08</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" ref="L8:L22" si="0">K8*0.5</f>
-        <v>0.5</v>
+        <f>K8*0.5</f>
+        <v>1.075</v>
       </c>
       <c r="M8" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N8" s="6">
         <f>M8/10</f>
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O8" s="6">
-        <f>G8+J8+L8</f>
-        <v>1.2650000000000001</v>
+        <f t="shared" ref="O8:O22" si="0">G8+J8+L8</f>
+        <v>3.4240000000000004</v>
       </c>
       <c r="P8" s="6">
-        <f>INT(O8*10)/10+IF(MOD(O8*10,1)&gt;=0.5,0.1,0)</f>
-        <v>1.3</v>
-      </c>
-      <c r="Q8" s="1">
-        <f>IF(O8&lt;3,3-O8,"No aplica")</f>
-        <v>1.7349999999999999</v>
-      </c>
-      <c r="R8" s="1">
-        <f>P8+N8</f>
-        <v>1.4000000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <f t="shared" ref="P8:P22" si="1">INT(O8*10)/10+IF(MOD(O8*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.4</v>
+      </c>
+      <c r="Q8" s="1" t="str">
+        <f t="shared" ref="Q8:Q22" si="2">IF(O8&lt;3,3-O8,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>1013264286</v>
       </c>
@@ -4724,46 +4554,52 @@
         <v>26</v>
       </c>
       <c r="D9" s="21"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1.6</v>
+      </c>
       <c r="G9" s="1">
-        <f t="shared" ref="G9:G22" si="1">(E9*0.35+F9*0.65)*0.1</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="5" t="e">
-        <f>AVERAGE(H9:I9)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="1"/>
+        <f t="shared" ref="G9:G22" si="3">(E9*0.35+F9*0.65)*0.1</f>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" ref="J9:J22" si="4">(AVERAGE(H9:I9)+N9)*0.4</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
       <c r="L9" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L9:L22" si="5">K9*0.5</f>
         <v>0</v>
       </c>
       <c r="M9" s="17"/>
       <c r="N9" s="6">
-        <f t="shared" ref="N9:N22" si="2">M9/10</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="6" t="e">
-        <f>G9+J9+L9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P9" s="6" t="e">
-        <f>INT(O9*10)/10+IF(MOD(O9*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q9" s="1" t="e">
-        <f>IF(O9&lt;3,3-O9,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" s="1" t="e">
-        <f t="shared" ref="R9:R22" si="3">P9+N9</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <f t="shared" ref="N9:N22" si="6">M9/10</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" si="0"/>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="Q9" s="1">
+        <f t="shared" si="2"/>
+        <v>2.8784999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>1013267876</v>
       </c>
@@ -4772,46 +4608,52 @@
         <v>28</v>
       </c>
       <c r="D10" s="21"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="E10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3.6</v>
+      </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="5" t="e">
-        <f>AVERAGE(H10:I10)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K10" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.2515</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="4"/>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3</v>
+      </c>
       <c r="L10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.5</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" si="0"/>
+        <v>3.5115000000000003</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="Q10" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="6" t="e">
-        <f>G10+J10+L10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P10" s="6" t="e">
-        <f>INT(O10*10)/10+IF(MOD(O10*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q10" s="1" t="e">
-        <f>IF(O10&lt;3,3-O10,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>1014991121</v>
       </c>
@@ -4820,46 +4662,52 @@
         <v>30</v>
       </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3.5</v>
+      </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="5" t="e">
-        <f>AVERAGE(H11:I11)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.245</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="4"/>
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
       <c r="L11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" si="0"/>
+        <v>2.9450000000000003</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="1"/>
+        <v>2.9</v>
+      </c>
+      <c r="Q11" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="6" t="e">
-        <f>G11+J11+L11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" s="6" t="e">
-        <f>INT(O11*10)/10+IF(MOD(O11*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q11" s="1" t="e">
-        <f>IF(O11&lt;3,3-O11,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R11" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>5.4999999999999716E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>1022961365</v>
       </c>
@@ -4868,46 +4716,52 @@
         <v>32</v>
       </c>
       <c r="D12" s="21"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="E12" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3.5</v>
+      </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="5" t="e">
-        <f>AVERAGE(H12:I12)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K12" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.35350000000000004</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="4"/>
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.2</v>
+      </c>
       <c r="L12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.6</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="0"/>
+        <v>3.8535000000000004</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+      <c r="Q12" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="6" t="e">
-        <f>G12+J12+L12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P12" s="6" t="e">
-        <f>INT(O12*10)/10+IF(MOD(O12*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q12" s="1" t="e">
-        <f>IF(O12&lt;3,3-O12,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R12" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>1033714140</v>
       </c>
@@ -4916,46 +4770,52 @@
         <v>34</v>
       </c>
       <c r="D13" s="21"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="E13" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>3</v>
+      </c>
       <c r="G13" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="5" t="e">
-        <f>AVERAGE(H13:I13)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K13" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.24750000000000003</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2.4</v>
+      </c>
       <c r="L13" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.2</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" si="0"/>
+        <v>3.4474999999999998</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="1"/>
+        <v>3.4</v>
+      </c>
+      <c r="Q13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="6" t="e">
-        <f>G13+J13+L13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P13" s="6" t="e">
-        <f>INT(O13*10)/10+IF(MOD(O13*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q13" s="1" t="e">
-        <f>IF(O13&lt;3,3-O13,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R13" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>1013122283</v>
       </c>
@@ -4964,46 +4824,52 @@
         <v>36</v>
       </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="E14" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2.5</v>
+      </c>
       <c r="G14" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="5" t="e">
-        <f>AVERAGE(H14:I14)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.16950000000000001</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="4"/>
+        <v>1.8800000000000001</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="L14" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="6">
+        <f t="shared" si="0"/>
+        <v>2.5994999999999999</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q14" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="6" t="e">
-        <f>G14+J14+L14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P14" s="6" t="e">
-        <f>INT(O14*10)/10+IF(MOD(O14*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q14" s="1" t="e">
-        <f>IF(O14&lt;3,3-O14,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R14" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>0.40050000000000008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>1094051548</v>
       </c>
@@ -5012,46 +4878,54 @@
         <v>38</v>
       </c>
       <c r="D15" s="21"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="E15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3.2</v>
+      </c>
       <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0.21850000000000003</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="4"/>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="5"/>
+        <v>1.4</v>
+      </c>
+      <c r="M15" s="6">
+        <v>6</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="6"/>
+        <v>0.6</v>
+      </c>
+      <c r="O15" s="6">
+        <f t="shared" si="0"/>
+        <v>3.4584999999999999</v>
+      </c>
+      <c r="P15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="5" t="e">
-        <f>AVERAGE(H15:I15)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="Q15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="6" t="e">
-        <f>G15+J15+L15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P15" s="6" t="e">
-        <f>INT(O15*10)/10+IF(MOD(O15*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q15" s="1" t="e">
-        <f>IF(O15&lt;3,3-O15,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R15" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>1031813370</v>
       </c>
@@ -5060,46 +4934,52 @@
         <v>40</v>
       </c>
       <c r="D16" s="21"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="E16" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4.3</v>
+      </c>
       <c r="G16" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="5" t="e">
-        <f>AVERAGE(H16:I16)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.32850000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="4"/>
+        <v>1.56</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2.15</v>
+      </c>
       <c r="L16" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.075</v>
       </c>
       <c r="M16" s="6"/>
       <c r="N16" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
+        <f t="shared" si="0"/>
+        <v>2.9634999999999998</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Q16" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="6" t="e">
-        <f>G16+J16+L16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P16" s="6" t="e">
-        <f>INT(O16*10)/10+IF(MOD(O16*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q16" s="1" t="e">
-        <f>IF(O16&lt;3,3-O16,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R16" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>3.6500000000000199E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>1034295843</v>
       </c>
@@ -5108,48 +4988,54 @@
         <v>42</v>
       </c>
       <c r="D17" s="21"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="E17" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4.3</v>
+      </c>
       <c r="G17" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="5" t="e">
-        <f>AVERAGE(H17:I17)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K17" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.33550000000000002</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="4"/>
+        <v>2.3200000000000003</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="L17" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.1499999999999999</v>
       </c>
       <c r="M17" s="6">
         <v>9</v>
       </c>
       <c r="N17" s="6">
+        <f t="shared" si="6"/>
+        <v>0.9</v>
+      </c>
+      <c r="O17" s="6">
+        <f t="shared" si="0"/>
+        <v>3.8055000000000003</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+      <c r="Q17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-      <c r="O17" s="6" t="e">
-        <f>G17+J17+L17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P17" s="6" t="e">
-        <f>INT(O17*10)/10+IF(MOD(O17*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q17" s="1" t="e">
-        <f>IF(O17&lt;3,3-O17,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R17" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>1095551423</v>
       </c>
@@ -5158,46 +5044,52 @@
         <v>44</v>
       </c>
       <c r="D18" s="21"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="E18" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3.9</v>
+      </c>
       <c r="G18" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="5" t="e">
-        <f>AVERAGE(H18:I18)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K18" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="4"/>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="K18" s="1">
+        <v>3</v>
+      </c>
       <c r="L18" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.5</v>
       </c>
       <c r="M18" s="6"/>
       <c r="N18" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="6">
+        <f t="shared" si="0"/>
+        <v>3.524</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="Q18" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="6" t="e">
-        <f>G18+J18+L18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P18" s="6" t="e">
-        <f>INT(O18*10)/10+IF(MOD(O18*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q18" s="1" t="e">
-        <f>IF(O18&lt;3,3-O18,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R18" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>1087802193</v>
       </c>
@@ -5206,48 +5098,54 @@
         <v>46</v>
       </c>
       <c r="D19" s="21"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="E19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3.2</v>
+      </c>
       <c r="G19" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="5" t="e">
-        <f>AVERAGE(H19:I19)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K19" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="4"/>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2.5</v>
+      </c>
       <c r="L19" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.25</v>
       </c>
       <c r="M19" s="6">
         <v>9</v>
       </c>
       <c r="N19" s="6">
+        <f t="shared" si="6"/>
+        <v>0.9</v>
+      </c>
+      <c r="O19" s="6">
+        <f t="shared" si="0"/>
+        <v>3.7755000000000001</v>
+      </c>
+      <c r="P19" s="6">
+        <f t="shared" si="1"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="Q19" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0.9</v>
-      </c>
-      <c r="O19" s="6" t="e">
-        <f>G19+J19+L19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P19" s="6" t="e">
-        <f>INT(O19*10)/10+IF(MOD(O19*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q19" s="1" t="e">
-        <f>IF(O19&lt;3,3-O19,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R19" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>1072747164</v>
       </c>
@@ -5256,48 +5154,54 @@
         <v>48</v>
       </c>
       <c r="D20" s="21"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="E20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="G20" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="5" t="e">
-        <f>AVERAGE(H20:I20)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K20" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="4"/>
+        <v>1.2800000000000002</v>
+      </c>
+      <c r="K20" s="1">
+        <v>3.25</v>
+      </c>
       <c r="L20" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.625</v>
       </c>
       <c r="M20" s="6">
         <v>7</v>
       </c>
       <c r="N20" s="6">
+        <f t="shared" si="6"/>
+        <v>0.7</v>
+      </c>
+      <c r="O20" s="6">
+        <f t="shared" si="0"/>
+        <v>3.1890000000000001</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" si="1"/>
+        <v>3.2</v>
+      </c>
+      <c r="Q20" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0.7</v>
-      </c>
-      <c r="O20" s="6" t="e">
-        <f>G20+J20+L20</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P20" s="6" t="e">
-        <f>INT(O20*10)/10+IF(MOD(O20*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q20" s="1" t="e">
-        <f>IF(O20&lt;3,3-O20,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R20" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>1075234817</v>
       </c>
@@ -5306,46 +5210,52 @@
         <v>50</v>
       </c>
       <c r="D21" s="21"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
       <c r="G21" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="5" t="e">
-        <f>AVERAGE(H21:I21)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1">
+        <v>5</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="4"/>
+        <v>1.8</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1.8</v>
+      </c>
       <c r="L21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>0.9</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="6">
+        <f t="shared" si="0"/>
+        <v>2.7</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="Q21" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="6" t="e">
-        <f>G21+J21+L21</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P21" s="6" t="e">
-        <f>INT(O21*10)/10+IF(MOD(O21*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q21" s="1" t="e">
-        <f>IF(O21&lt;3,3-O21,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R21" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>0.29999999999999982</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>1016912717</v>
       </c>
@@ -5354,43 +5264,49 @@
         <v>51</v>
       </c>
       <c r="D22" s="21"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="E22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1.3</v>
+      </c>
       <c r="G22" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="5" t="e">
-        <f>AVERAGE(H22:I22)*0.4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K22" s="1"/>
+        <f t="shared" si="3"/>
+        <v>0.10200000000000001</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="4"/>
+        <v>1.92</v>
+      </c>
+      <c r="K22" s="1">
+        <v>3.75</v>
+      </c>
       <c r="L22" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1.875</v>
       </c>
       <c r="M22" s="6"/>
       <c r="N22" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="6">
+        <f t="shared" si="0"/>
+        <v>3.8969999999999998</v>
+      </c>
+      <c r="P22" s="6">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+      <c r="Q22" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="6" t="e">
-        <f>G22+J22+L22</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P22" s="6" t="e">
-        <f>INT(O22*10)/10+IF(MOD(O22*10,1)&gt;=0.5,0.1,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q22" s="1" t="e">
-        <f>IF(O22&lt;3,3-O22,"No aplica")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R22" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>No aplica</v>
       </c>
     </row>
   </sheetData>
@@ -5439,62 +5355,44 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:D22"/>
   </mergeCells>
-  <conditionalFormatting sqref="H8:I21">
-    <cfRule type="expression" dxfId="11" priority="18">
+  <conditionalFormatting sqref="E8:F22">
+    <cfRule type="expression" dxfId="9" priority="5">
+      <formula>E8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>E8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:I22">
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>H8&gt;=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>H8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:I21">
-    <cfRule type="expression" dxfId="10" priority="17">
-      <formula>H8&gt;=3</formula>
+  <conditionalFormatting sqref="K8:K22">
+    <cfRule type="expression" dxfId="5" priority="15">
+      <formula>K8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K22">
-    <cfRule type="expression" dxfId="9" priority="16">
+    <cfRule type="expression" dxfId="4" priority="16">
       <formula>K8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K22">
-    <cfRule type="expression" dxfId="8" priority="15">
-      <formula>K8&gt;=3</formula>
+  <conditionalFormatting sqref="M8:M22">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22">
-    <cfRule type="expression" dxfId="7" priority="10">
-      <formula>H22&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22">
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>H22&gt;=3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:F22">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>E8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:F22">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>E8&gt;=3</formula>
+    <cfRule type="containsBlanks" dxfId="2" priority="2">
+      <formula>LEN(TRIM(M8))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8:O22">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>O8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O22">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>O8&gt;=3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M8:M22">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(M8))=0</formula>
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>O8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Corte_3.xlsx
+++ b/Corte_3.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185550E2-598D-4B2E-AB82-D62DD59E97B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="994" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75DC8D28-CAE7-4731-98F5-BBA64923177B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corte" sheetId="1" r:id="rId1"/>
@@ -239,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,19 +454,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -486,20 +484,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -509,6 +501,9 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -523,27 +518,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="48">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -561,6 +536,16 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -726,6 +711,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -741,6 +756,16 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -826,6 +851,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -836,11 +901,51 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="3"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -891,16 +996,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1240,7 +1335,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" customWidth="1"/>
@@ -1252,56 +1347,56 @@
     <col min="24" max="24" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23" t="s">
+    <row r="1" spans="1:27">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="35"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
@@ -1309,44 +1404,44 @@
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:27">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="14">
         <v>0.1</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="3">
         <v>0.4</v>
       </c>
@@ -1356,13 +1451,13 @@
       <c r="O6" s="4">
         <v>0.5</v>
       </c>
-      <c r="P6" s="33" t="s">
+      <c r="P6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="35"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="34"/>
       <c r="U6" s="12" t="s">
         <v>13</v>
       </c>
@@ -1376,15 +1471,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+    <row r="7" spans="1:27">
+      <c r="A7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -1428,15 +1523,15 @@
       <c r="W7" s="11"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:27">
+      <c r="A8" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="21"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
         <f>E8*0.1</f>
@@ -1479,15 +1574,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:27">
+      <c r="A9" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="21"/>
+      <c r="D9" s="31"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
         <f t="shared" ref="F9:F22" si="2">E9*0.1</f>
@@ -1530,15 +1625,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:27">
+      <c r="A10" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="21"/>
+      <c r="D10" s="31"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
         <f t="shared" si="2"/>
@@ -1581,15 +1676,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:27">
+      <c r="A11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="21"/>
+      <c r="D11" s="31"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
         <f t="shared" si="2"/>
@@ -1632,15 +1727,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:27">
+      <c r="A12" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="21"/>
+      <c r="D12" s="31"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
         <f t="shared" si="2"/>
@@ -1684,15 +1779,15 @@
       </c>
       <c r="AA12" s="8"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:27">
+      <c r="A13" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="21"/>
+      <c r="D13" s="31"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
         <f t="shared" si="2"/>
@@ -1735,15 +1830,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:27">
+      <c r="A14" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="21"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1">
         <f t="shared" si="2"/>
@@ -1786,15 +1881,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:27">
+      <c r="A15" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
+      <c r="B15" s="30"/>
+      <c r="C15" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="21"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1">
         <f t="shared" si="2"/>
@@ -1837,15 +1932,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:27">
+      <c r="A16" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="21"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
         <f t="shared" si="2"/>
@@ -1888,15 +1983,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:24">
+      <c r="A17" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="21"/>
+      <c r="D17" s="31"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
         <f t="shared" si="2"/>
@@ -1939,15 +2034,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+    <row r="18" spans="1:24">
+      <c r="A18" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="21"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1">
         <f t="shared" si="2"/>
@@ -1990,15 +2085,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:24">
+      <c r="A19" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21" t="s">
+      <c r="B19" s="30"/>
+      <c r="C19" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="21"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1">
         <f t="shared" si="2"/>
@@ -2041,15 +2136,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+    <row r="20" spans="1:24">
+      <c r="A20" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
+      <c r="B20" s="30"/>
+      <c r="C20" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="21"/>
+      <c r="D20" s="31"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1">
         <f t="shared" si="2"/>
@@ -2092,15 +2187,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:24">
+      <c r="A21" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21" t="s">
+      <c r="B21" s="30"/>
+      <c r="C21" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="21"/>
+      <c r="D21" s="31"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1">
         <f t="shared" si="2"/>
@@ -2143,15 +2238,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
+    <row r="22" spans="1:24">
+      <c r="A22" s="29">
         <v>1016912717</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21" t="s">
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="21"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1">
         <f t="shared" si="2"/>
@@ -2200,6 +2295,33 @@
     <filterColumn colId="2" showButton="0"/>
   </autoFilter>
   <mergeCells count="43">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="P6:T6"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="G6:L6"/>
@@ -2216,72 +2338,75 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
   </mergeCells>
+  <conditionalFormatting sqref="G8:L21">
+    <cfRule type="expression" dxfId="47" priority="14">
+      <formula>G8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:L21">
+    <cfRule type="expression" dxfId="46" priority="13">
+      <formula>G8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N8:N22">
+    <cfRule type="expression" dxfId="45" priority="12">
+      <formula>N8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N8:N22">
+    <cfRule type="expression" dxfId="44" priority="11">
+      <formula>N8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V8:V22">
+    <cfRule type="expression" dxfId="43" priority="10">
+      <formula>V8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V8:V22">
+    <cfRule type="expression" dxfId="42" priority="9">
+      <formula>V8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8:T21">
+    <cfRule type="containsBlanks" dxfId="41" priority="8">
+      <formula>LEN(TRIM(P8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8:T21">
+    <cfRule type="cellIs" dxfId="40" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:L22">
+    <cfRule type="expression" dxfId="39" priority="6">
+      <formula>G22&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:L22">
+    <cfRule type="expression" dxfId="38" priority="5">
+      <formula>G22&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22:T22">
+    <cfRule type="containsBlanks" dxfId="37" priority="4">
+      <formula>LEN(TRIM(P22))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22:T22">
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E8:E22">
-    <cfRule type="expression" dxfId="37" priority="1">
-      <formula>E8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>E8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:L22">
-    <cfRule type="expression" dxfId="35" priority="5">
-      <formula>G8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="6">
-      <formula>G8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N22">
-    <cfRule type="expression" dxfId="33" priority="11">
-      <formula>N8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="12">
-      <formula>N8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:T22">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="30" priority="4">
-      <formula>LEN(TRIM(P8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V22">
-    <cfRule type="expression" dxfId="29" priority="9">
-      <formula>V8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="10">
-      <formula>V8&lt;3</formula>
+  <conditionalFormatting sqref="E8:E22">
+    <cfRule type="expression" dxfId="34" priority="1">
+      <formula>E8&gt;=3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2291,7 +2416,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865D47EF-51ED-406F-A091-BAA11C63147F}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="4" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -2305,25 +2430,25 @@
     <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="36" t="s">
         <v>3</v>
       </c>
@@ -2333,25 +2458,25 @@
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:17">
+      <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="37"/>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="22"/>
+      <c r="B4" s="19"/>
       <c r="C4" s="38" t="s">
         <v>7</v>
       </c>
@@ -2361,23 +2486,23 @@
       <c r="G4" s="38"/>
       <c r="H4" s="38"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+    <row r="6" spans="1:17">
+      <c r="A6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="14">
         <v>0.1</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="24"/>
+      <c r="H6" s="25"/>
       <c r="I6" s="3">
         <v>0.4</v>
       </c>
@@ -2406,15 +2531,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+    <row r="7" spans="1:17">
+      <c r="A7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -2435,20 +2560,20 @@
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:17">
+      <c r="A8" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="21"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" ref="F8:F22" si="0">E8*0.1</f>
+        <f>E8*0.1</f>
         <v>0.5</v>
       </c>
       <c r="G8" s="1">
@@ -2465,7 +2590,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" ref="K8:K22" si="1">J8*0.5</f>
+        <f>J8*0.5</f>
         <v>1.7</v>
       </c>
       <c r="L8" s="6"/>
@@ -2474,15 +2599,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" ref="N8:N22" si="2">F8+I8+K8</f>
+        <f>F8+I8+K8</f>
         <v>4.0600000000000005</v>
       </c>
       <c r="O8" s="6">
-        <f t="shared" ref="O8:O22" si="3">INT(N8*10)/10+IF(MOD(N8*10,1)&gt;=0.5,0.1,0)</f>
+        <f>INT(N8*10)/10+IF(MOD(N8*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="P8" s="1" t="str">
-        <f t="shared" ref="P8:P22" si="4">IF(N8&lt;3,3-N8,"No aplica")</f>
+        <f>IF(N8&lt;3,3-N8,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q8" s="1">
@@ -2490,20 +2615,20 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:17">
+      <c r="A9" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="21"/>
+      <c r="D9" s="31"/>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="0"/>
+        <f>E9*0.1</f>
         <v>0.5</v>
       </c>
       <c r="G9" s="1">
@@ -2513,14 +2638,14 @@
         <v>4.5</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" ref="I9:I21" si="5">(G9*0.3+H9*0.7)*0.4</f>
+        <f t="shared" ref="I9:I22" si="0">(G9*0.3+H9*0.7)*0.4</f>
         <v>1.8600000000000003</v>
       </c>
       <c r="J9" s="1">
         <v>2.9</v>
       </c>
       <c r="K9" s="6">
-        <f t="shared" si="1"/>
+        <f>J9*0.5</f>
         <v>1.45</v>
       </c>
       <c r="L9" s="6">
@@ -2531,36 +2656,36 @@
         <v>0.15</v>
       </c>
       <c r="N9" s="6">
-        <f t="shared" si="2"/>
+        <f>F9+I9+K9</f>
         <v>3.8100000000000005</v>
       </c>
       <c r="O9" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N9*10)/10+IF(MOD(N9*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.8</v>
       </c>
       <c r="P9" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N9&lt;3,3-N9,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" ref="Q9:Q22" si="6">O9+M9</f>
+        <f t="shared" ref="Q9:Q22" si="1">O9+M9</f>
         <v>3.9499999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:17">
+      <c r="A10" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="21"/>
+      <c r="D10" s="31"/>
       <c r="E10" s="1">
         <v>3.5</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="0"/>
+        <f>E10*0.1</f>
         <v>0.35000000000000003</v>
       </c>
       <c r="G10" s="1">
@@ -2570,52 +2695,52 @@
         <v>4.2</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.7759999999999998</v>
       </c>
       <c r="J10" s="1">
         <v>3.25</v>
       </c>
       <c r="K10" s="6">
-        <f t="shared" si="1"/>
+        <f>J10*0.5</f>
         <v>1.625</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6">
-        <f t="shared" ref="M10:M22" si="7">L10/10</f>
+        <f t="shared" ref="M10:M22" si="2">L10/10</f>
         <v>0</v>
       </c>
       <c r="N10" s="6">
-        <f t="shared" si="2"/>
+        <f>F10+I10+K10</f>
         <v>3.7509999999999999</v>
       </c>
       <c r="O10" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N10*10)/10+IF(MOD(N10*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.8000000000000003</v>
       </c>
       <c r="P10" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N10&lt;3,3-N10,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>3.8000000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:17">
+      <c r="A11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="21"/>
+      <c r="D11" s="31"/>
       <c r="E11" s="1">
         <v>3.1</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="0"/>
+        <f>E11*0.1</f>
         <v>0.31000000000000005</v>
       </c>
       <c r="G11" s="1">
@@ -2625,54 +2750,54 @@
         <v>4.2</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.7759999999999998</v>
       </c>
       <c r="J11" s="1">
         <v>4.4000000000000004</v>
       </c>
       <c r="K11" s="6">
-        <f t="shared" si="1"/>
+        <f>J11*0.5</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="L11" s="6">
         <v>1.5</v>
       </c>
       <c r="M11" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N11" s="6">
-        <f t="shared" si="2"/>
+        <f>F11+I11+K11</f>
         <v>4.2859999999999996</v>
       </c>
       <c r="O11" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N11*10)/10+IF(MOD(N11*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.3</v>
       </c>
       <c r="P11" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N11&lt;3,3-N11,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.45</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:17">
+      <c r="A12" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="21"/>
+      <c r="D12" s="31"/>
       <c r="E12" s="1">
         <v>3.4</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="0"/>
+        <f>E12*0.1</f>
         <v>0.34</v>
       </c>
       <c r="G12" s="1">
@@ -2682,54 +2807,54 @@
         <v>4.8</v>
       </c>
       <c r="I12" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.944</v>
       </c>
       <c r="J12" s="1">
         <v>3.7</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="1"/>
+        <f>J12*0.5</f>
         <v>1.85</v>
       </c>
       <c r="L12" s="6">
         <v>1.5</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="2"/>
+        <f>F12+I12+K12</f>
         <v>4.1340000000000003</v>
       </c>
       <c r="O12" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N12*10)/10+IF(MOD(N12*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="P12" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N12&lt;3,3-N12,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:17">
+      <c r="A13" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="21"/>
+      <c r="D13" s="31"/>
       <c r="E13" s="1">
         <v>3.5</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="0"/>
+        <f>E13*0.1</f>
         <v>0.35000000000000003</v>
       </c>
       <c r="G13" s="1">
@@ -2739,54 +2864,54 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.8320000000000001</v>
       </c>
       <c r="J13" s="1">
         <v>3.98</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="1"/>
+        <f>J13*0.5</f>
         <v>1.99</v>
       </c>
       <c r="L13" s="6">
         <v>1.5</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="2"/>
+        <f>F13+I13+K13</f>
         <v>4.1719999999999997</v>
       </c>
       <c r="O13" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N13*10)/10+IF(MOD(N13*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.1999999999999993</v>
       </c>
       <c r="P13" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N13&lt;3,3-N13,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+    <row r="14" spans="1:17">
+      <c r="A14" s="29">
         <v>1016912717</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="21"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="1">
         <v>2.8</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="0"/>
+        <f>E14*0.1</f>
         <v>0.27999999999999997</v>
       </c>
       <c r="G14" s="1">
@@ -2796,54 +2921,54 @@
         <v>5</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J14" s="1">
         <v>4.7549999999999999</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="1"/>
+        <f>J14*0.5</f>
         <v>2.3774999999999999</v>
       </c>
       <c r="L14" s="6">
         <v>1.5</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="2"/>
+        <f>F14+I14+K14</f>
         <v>4.6574999999999998</v>
       </c>
       <c r="O14" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N14*10)/10+IF(MOD(N14*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.6999999999999993</v>
       </c>
       <c r="P14" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N14&lt;3,3-N14,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:17">
+      <c r="A15" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
+      <c r="B15" s="30"/>
+      <c r="C15" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="21"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="1">
         <v>3.7</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="0"/>
+        <f>E15*0.1</f>
         <v>0.37000000000000005</v>
       </c>
       <c r="G15" s="1">
@@ -2853,54 +2978,54 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.8320000000000001</v>
       </c>
       <c r="J15" s="1">
         <v>3.65</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="1"/>
+        <f>J15*0.5</f>
         <v>1.825</v>
       </c>
       <c r="L15" s="6">
         <v>1.5</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="2"/>
+        <f>F15+I15+K15</f>
         <v>4.0270000000000001</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N15*10)/10+IF(MOD(N15*10,1)&gt;=0.5,0.1,0)</f>
         <v>4</v>
       </c>
       <c r="P15" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N15&lt;3,3-N15,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:17">
+      <c r="A16" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="21"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="0"/>
+        <f>E16*0.1</f>
         <v>0.2</v>
       </c>
       <c r="G16" s="1">
@@ -2910,54 +3035,54 @@
         <v>4</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.72</v>
       </c>
       <c r="J16" s="1">
         <v>2.2999999999999998</v>
       </c>
       <c r="K16" s="6">
-        <f t="shared" si="1"/>
+        <f>J16*0.5</f>
         <v>1.1499999999999999</v>
       </c>
       <c r="L16" s="6">
         <v>2.5</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="N16" s="6">
-        <f t="shared" si="2"/>
+        <f>F16+I16+K16</f>
         <v>3.07</v>
       </c>
       <c r="O16" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N16*10)/10+IF(MOD(N16*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.1</v>
       </c>
       <c r="P16" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N16&lt;3,3-N16,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>3.35</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:17">
+      <c r="A17" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="21"/>
+      <c r="D17" s="31"/>
       <c r="E17" s="1">
         <v>3.4</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="0"/>
+        <f>E17*0.1</f>
         <v>0.34</v>
       </c>
       <c r="G17" s="1">
@@ -2967,54 +3092,54 @@
         <v>4.8</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.944</v>
       </c>
       <c r="J17" s="1">
         <v>4.8499999999999996</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="1"/>
+        <f>J17*0.5</f>
         <v>2.4249999999999998</v>
       </c>
       <c r="L17" s="6">
         <v>1.5</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="2"/>
+        <f>F17+I17+K17</f>
         <v>4.7089999999999996</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N17*10)/10+IF(MOD(N17*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.7</v>
       </c>
       <c r="P17" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N17&lt;3,3-N17,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.8500000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+    <row r="18" spans="1:17">
+      <c r="A18" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="21"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="1">
         <v>3.2</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="0"/>
+        <f>E18*0.1</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="G18" s="1">
@@ -3024,54 +3149,54 @@
         <v>4.5</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.8600000000000003</v>
       </c>
       <c r="J18" s="1">
         <v>4.5999999999999996</v>
       </c>
       <c r="K18" s="6">
-        <f t="shared" si="1"/>
+        <f>J18*0.5</f>
         <v>2.2999999999999998</v>
       </c>
       <c r="L18" s="6">
         <v>1.5</v>
       </c>
       <c r="M18" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N18" s="6">
-        <f t="shared" si="2"/>
+        <f>F18+I18+K18</f>
         <v>4.4800000000000004</v>
       </c>
       <c r="O18" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N18*10)/10+IF(MOD(N18*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.5</v>
       </c>
       <c r="P18" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N18&lt;3,3-N18,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q18" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:17">
+      <c r="A19" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21" t="s">
+      <c r="B19" s="30"/>
+      <c r="C19" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="21"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="1">
         <v>1.8</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="0"/>
+        <f>E19*0.1</f>
         <v>0.18000000000000002</v>
       </c>
       <c r="G19" s="1">
@@ -3081,52 +3206,52 @@
         <v>4.8</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.944</v>
       </c>
       <c r="J19" s="1">
         <v>2.4500000000000002</v>
       </c>
       <c r="K19" s="6">
-        <f t="shared" si="1"/>
+        <f>J19*0.5</f>
         <v>1.2250000000000001</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="2"/>
+        <f>F19+I19+K19</f>
         <v>3.3490000000000002</v>
       </c>
       <c r="O19" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N19*10)/10+IF(MOD(N19*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.3</v>
       </c>
       <c r="P19" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N19&lt;3,3-N19,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q19" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>3.3</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+    <row r="20" spans="1:17">
+      <c r="A20" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
+      <c r="B20" s="30"/>
+      <c r="C20" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="21"/>
+      <c r="D20" s="31"/>
       <c r="E20" s="1">
         <v>2.6</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="0"/>
+        <f>E20*0.1</f>
         <v>0.26</v>
       </c>
       <c r="G20" s="1">
@@ -3136,54 +3261,54 @@
         <v>5</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J20" s="1">
         <v>3.85</v>
       </c>
       <c r="K20" s="6">
-        <f t="shared" si="1"/>
+        <f>J20*0.5</f>
         <v>1.925</v>
       </c>
       <c r="L20" s="6">
         <v>1.5</v>
       </c>
       <c r="M20" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="N20" s="6">
-        <f t="shared" si="2"/>
+        <f>F20+I20+K20</f>
         <v>4.1849999999999996</v>
       </c>
       <c r="O20" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N20*10)/10+IF(MOD(N20*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.1999999999999993</v>
       </c>
       <c r="P20" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N20&lt;3,3-N20,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q20" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:17">
+      <c r="A21" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21" t="s">
+      <c r="B21" s="30"/>
+      <c r="C21" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="21"/>
+      <c r="D21" s="31"/>
       <c r="E21" s="1">
         <v>3.9</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="0"/>
+        <f>E21*0.1</f>
         <v>0.39</v>
       </c>
       <c r="G21" s="1">
@@ -3193,52 +3318,52 @@
         <v>4.8</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>1.944</v>
       </c>
       <c r="J21" s="1">
         <v>3</v>
       </c>
       <c r="K21" s="6">
-        <f t="shared" si="1"/>
+        <f>J21*0.5</f>
         <v>1.5</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N21" s="6">
-        <f t="shared" si="2"/>
+        <f>F21+I21+K21</f>
         <v>3.8340000000000001</v>
       </c>
       <c r="O21" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N21*10)/10+IF(MOD(N21*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.8</v>
       </c>
       <c r="P21" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N21&lt;3,3-N21,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q21" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+    <row r="22" spans="1:17">
+      <c r="A22" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21" t="s">
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="21"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="1">
         <v>2.5</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="0"/>
+        <f>E22*0.1</f>
         <v>0.25</v>
       </c>
       <c r="G22" s="1">
@@ -3255,28 +3380,28 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="1"/>
+        <f>J22*0.5</f>
         <v>2.1749999999999998</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N22" s="6">
-        <f t="shared" si="2"/>
+        <f>F22+I22+K22</f>
         <v>4.2009999999999996</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" si="3"/>
+        <f>INT(N22*10)/10+IF(MOD(N22*10,1)&gt;=0.5,0.1,0)</f>
         <v>4.2</v>
       </c>
       <c r="P22" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N22&lt;3,3-N22,"No aplica")</f>
         <v>No aplica</v>
       </c>
       <c r="Q22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>4.2</v>
       </c>
     </row>
@@ -3289,6 +3414,36 @@
     </sortState>
   </autoFilter>
   <mergeCells count="42">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A1:B1"/>
@@ -3301,6 +3456,963 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="G6:H6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G8:H21">
+    <cfRule type="expression" dxfId="33" priority="16">
+      <formula>G8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:H21">
+    <cfRule type="expression" dxfId="32" priority="15">
+      <formula>G8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8:J22">
+    <cfRule type="expression" dxfId="31" priority="14">
+      <formula>J8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8:J22">
+    <cfRule type="expression" dxfId="30" priority="13">
+      <formula>J8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N8:N22">
+    <cfRule type="expression" dxfId="29" priority="12">
+      <formula>N8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N8:N22">
+    <cfRule type="expression" dxfId="28" priority="11">
+      <formula>N8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:H22">
+    <cfRule type="expression" dxfId="27" priority="8">
+      <formula>G22&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:H22">
+    <cfRule type="expression" dxfId="26" priority="7">
+      <formula>G22&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E22">
+    <cfRule type="expression" dxfId="25" priority="4">
+      <formula>E8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E22">
+    <cfRule type="expression" dxfId="24" priority="3">
+      <formula>E8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L8:L22">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="22" priority="2">
+      <formula>LEN(TRIM(L8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA64364-85F1-4B4C-B1BB-0179859BFB61}">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="1">
+        <f>(E8+F8)*0.1</f>
+        <v>0.41</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="I8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J8" s="5">
+        <f>AVERAGE(H8:I8)*0.4</f>
+        <v>1.6600000000000001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="L8" s="6">
+        <f>K8*0.5</f>
+        <v>1.9</v>
+      </c>
+      <c r="M8" s="6">
+        <f>G8+J8+L8</f>
+        <v>3.97</v>
+      </c>
+      <c r="N8" s="6">
+        <f>INT(M8*10)/10+IF(MOD(M8*10,1)&gt;=0.5,0.1,0)</f>
+        <v>4</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <f>IF(M8&lt;3,3-M8,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="31"/>
+      <c r="E9" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" ref="G9:G22" si="0">(E9+F9)*0.1</f>
+        <v>0.34</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J9" s="5">
+        <f>AVERAGE(H9:I9)*0.4</f>
+        <v>1.4800000000000002</v>
+      </c>
+      <c r="K9" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="L9" s="6">
+        <f>K9*0.5</f>
+        <v>1.125</v>
+      </c>
+      <c r="M9" s="6">
+        <f>G9+J9+L9</f>
+        <v>2.9450000000000003</v>
+      </c>
+      <c r="N9" s="6">
+        <f>INT(M9*10)/10+IF(MOD(M9*10,1)&gt;=0.5,0.1,0)</f>
+        <v>2.9</v>
+      </c>
+      <c r="O9" s="1">
+        <f>IF(M9&lt;3,3-M9,"No aplica")</f>
+        <v>5.4999999999999716E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J10" s="5">
+        <f>AVERAGE(H10:I10)*0.4</f>
+        <v>1.8600000000000003</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L10" s="6">
+        <f>K10*0.5</f>
+        <v>1.75</v>
+      </c>
+      <c r="M10" s="6">
+        <f>G10+J10+L10</f>
+        <v>3.7600000000000002</v>
+      </c>
+      <c r="N10" s="6">
+        <f>INT(M10*10)/10+IF(MOD(M10*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="O10" s="1" t="str">
+        <f>IF(M10&lt;3,3-M10,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="31"/>
+      <c r="E11" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.26</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J11" s="5">
+        <f>AVERAGE(H11:I11)*0.4</f>
+        <v>1.8600000000000003</v>
+      </c>
+      <c r="K11" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="L11" s="6">
+        <f>K11*0.5</f>
+        <v>1.8</v>
+      </c>
+      <c r="M11" s="6">
+        <f>G11+J11+L11</f>
+        <v>3.92</v>
+      </c>
+      <c r="N11" s="6">
+        <f>INT(M11*10)/10+IF(MOD(M11*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.9</v>
+      </c>
+      <c r="O11" s="1" t="str">
+        <f>IF(M11&lt;3,3-M11,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="31"/>
+      <c r="E12" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.38</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J12" s="5">
+        <f>AVERAGE(H12:I12)*0.4</f>
+        <v>1.8600000000000003</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="L12" s="6">
+        <f>K12*0.5</f>
+        <v>1.8</v>
+      </c>
+      <c r="M12" s="6">
+        <f>G12+J12+L12</f>
+        <v>4.04</v>
+      </c>
+      <c r="N12" s="6">
+        <f>INT(M12*10)/10+IF(MOD(M12*10,1)&gt;=0.5,0.1,0)</f>
+        <v>4</v>
+      </c>
+      <c r="O12" s="1" t="str">
+        <f>IF(M12&lt;3,3-M12,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="31"/>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <f>AVERAGE(H13:I13)*0.4</f>
+        <v>1.94</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="L13" s="6">
+        <f>K13*0.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="M13" s="6">
+        <f>G13+J13+L13</f>
+        <v>3.84</v>
+      </c>
+      <c r="N13" s="6">
+        <f>INT(M13*10)/10+IF(MOD(M13*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.8</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <f>IF(M13&lt;3,3-M13,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="29">
+        <v>1016912717</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="31"/>
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="5">
+        <f>AVERAGE(H14:I14)*0.4</f>
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L14" s="6">
+        <f>K14*0.5</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M14" s="6">
+        <f>G14+J14+L14</f>
+        <v>4.7</v>
+      </c>
+      <c r="N14" s="6">
+        <f>INT(M14*10)/10+IF(MOD(M14*10,1)&gt;=0.5,0.1,0)</f>
+        <v>4.7</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <f>IF(M14&lt;3,3-M14,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.34000000000000008</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5">
+        <f>AVERAGE(H15:I15)*0.4</f>
+        <v>1.9600000000000002</v>
+      </c>
+      <c r="K15" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="L15" s="6">
+        <f>K15*0.5</f>
+        <v>1.8</v>
+      </c>
+      <c r="M15" s="6">
+        <f>G15+J15+L15</f>
+        <v>4.1000000000000005</v>
+      </c>
+      <c r="N15" s="6">
+        <f>INT(M15*10)/10+IF(MOD(M15*10,1)&gt;=0.5,0.1,0)</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <f>IF(M15&lt;3,3-M15,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="J16" s="5">
+        <f>AVERAGE(H16:I16)*0.4</f>
+        <v>1.88</v>
+      </c>
+      <c r="K16" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="L16" s="6">
+        <f>K16*0.5</f>
+        <v>1.75</v>
+      </c>
+      <c r="M16" s="6">
+        <f>G16+J16+L16</f>
+        <v>3.92</v>
+      </c>
+      <c r="N16" s="6">
+        <f>INT(M16*10)/10+IF(MOD(M16*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.9</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <f>IF(M16&lt;3,3-M16,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="31"/>
+      <c r="E17" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I17" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J17" s="5">
+        <f>AVERAGE(H17:I17)*0.4</f>
+        <v>1.8600000000000003</v>
+      </c>
+      <c r="K17" s="1">
+        <v>3</v>
+      </c>
+      <c r="L17" s="6">
+        <f>K17*0.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="M17" s="6">
+        <f>G17+J17+L17</f>
+        <v>3.5900000000000003</v>
+      </c>
+      <c r="N17" s="6">
+        <f>INT(M17*10)/10+IF(MOD(M17*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.6</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <f>IF(M17&lt;3,3-M17,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="31"/>
+      <c r="E18" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="0"/>
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J18" s="5">
+        <f>AVERAGE(H18:I18)*0.4</f>
+        <v>1.9800000000000002</v>
+      </c>
+      <c r="K18" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="L18" s="6">
+        <f>K18*0.5</f>
+        <v>1.7</v>
+      </c>
+      <c r="M18" s="6">
+        <f>G18+J18+L18</f>
+        <v>4.17</v>
+      </c>
+      <c r="N18" s="6">
+        <f>INT(M18*10)/10+IF(MOD(M18*10,1)&gt;=0.5,0.1,0)</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <f>IF(M18&lt;3,3-M18,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="31"/>
+      <c r="E19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="5">
+        <f>AVERAGE(H19:I19)*0.4</f>
+        <v>1.9600000000000002</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="L19" s="6">
+        <f>K19*0.5</f>
+        <v>0.6</v>
+      </c>
+      <c r="M19" s="6">
+        <f>G19+J19+L19</f>
+        <v>2.6100000000000003</v>
+      </c>
+      <c r="N19" s="6">
+        <f>INT(M19*10)/10+IF(MOD(M19*10,1)&gt;=0.5,0.1,0)</f>
+        <v>2.6</v>
+      </c>
+      <c r="O19" s="1">
+        <f>IF(M19&lt;3,3-M19,"No aplica")</f>
+        <v>0.38999999999999968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="31"/>
+      <c r="E20" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="0"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="J20" s="5">
+        <f>AVERAGE(H20:I20)*0.4</f>
+        <v>1.99</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="L20" s="6">
+        <f>K20*0.5</f>
+        <v>0.9</v>
+      </c>
+      <c r="M20" s="6">
+        <f>G20+J20+L20</f>
+        <v>3.19</v>
+      </c>
+      <c r="N20" s="6">
+        <f>INT(M20*10)/10+IF(MOD(M20*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.2</v>
+      </c>
+      <c r="O20" s="1" t="str">
+        <f>IF(M20&lt;3,3-M20,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="31"/>
+      <c r="E21" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J21" s="5">
+        <f>AVERAGE(H21:I21)*0.4</f>
+        <v>1.74</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="L21" s="6">
+        <f>K21*0.5</f>
+        <v>1.45</v>
+      </c>
+      <c r="M21" s="6">
+        <f>G21+J21+L21</f>
+        <v>3.54</v>
+      </c>
+      <c r="N21" s="6">
+        <f>INT(M21*10)/10+IF(MOD(M21*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="O21" s="1" t="str">
+        <f>IF(M21&lt;3,3-M21,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="31"/>
+      <c r="E22" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4</v>
+      </c>
+      <c r="J22" s="5">
+        <f>AVERAGE(H22:I22)*0.4</f>
+        <v>1.8</v>
+      </c>
+      <c r="K22" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="L22" s="6">
+        <f>K22*0.5</f>
+        <v>1.6</v>
+      </c>
+      <c r="M22" s="6">
+        <f>G22+J22+L22</f>
+        <v>3.68</v>
+      </c>
+      <c r="N22" s="6">
+        <f>INT(M22*10)/10+IF(MOD(M22*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.7</v>
+      </c>
+      <c r="O22" s="1" t="str">
+        <f>IF(M22&lt;3,3-M22,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:O7" xr:uid="{FEA64364-85F1-4B4C-B1BB-0179859BFB61}">
+    <filterColumn colId="0" showButton="0"/>
+    <filterColumn colId="2" showButton="0"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:O22">
+      <sortCondition ref="C7"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="42">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A9:B9"/>
@@ -3332,144 +4444,154 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:D22"/>
   </mergeCells>
-  <conditionalFormatting sqref="E8:E22">
-    <cfRule type="expression" dxfId="27" priority="3">
-      <formula>E8&gt;=3</formula>
+  <conditionalFormatting sqref="H8:I21">
+    <cfRule type="expression" dxfId="21" priority="12">
+      <formula>H8&lt;3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="4">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:I21">
+    <cfRule type="expression" dxfId="20" priority="11">
+      <formula>H8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:K22">
+    <cfRule type="expression" dxfId="19" priority="10">
+      <formula>K8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:K22">
+    <cfRule type="expression" dxfId="18" priority="9">
+      <formula>K8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8:M22">
+    <cfRule type="expression" dxfId="17" priority="8">
+      <formula>M8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M8:M22">
+    <cfRule type="expression" dxfId="16" priority="7">
+      <formula>M8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22">
+    <cfRule type="expression" dxfId="15" priority="6">
+      <formula>H22&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22">
+    <cfRule type="expression" dxfId="14" priority="5">
+      <formula>H22&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:F22">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>E8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:H22">
-    <cfRule type="expression" dxfId="25" priority="7">
-      <formula>G8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="8">
-      <formula>G8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J22">
-    <cfRule type="expression" dxfId="23" priority="13">
-      <formula>J8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="14">
-      <formula>J8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L8:L22">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="containsBlanks" dxfId="20" priority="2">
-      <formula>LEN(TRIM(L8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N22">
-    <cfRule type="expression" dxfId="19" priority="11">
-      <formula>N8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="12">
-      <formula>N8&lt;3</formula>
+  <conditionalFormatting sqref="E8:F22">
+    <cfRule type="expression" dxfId="12" priority="3">
+      <formula>E8&gt;=3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA64364-85F1-4B4C-B1BB-0179859BFB61}">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D02CB94-BE69-462D-965B-A4EABD13502C}">
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" customWidth="1"/>
+    <col min="13" max="13" width="33" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="28"/>
       <c r="G6" s="14">
         <v>0.1</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="24"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="3">
         <v>0.4</v>
       </c>
@@ -3479,785 +4601,879 @@
       <c r="L6" s="4">
         <v>0.5</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="P6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+    <row r="7" spans="1:17">
+      <c r="A7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="9"/>
       <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
+      <c r="M7" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="N7" s="11"/>
-      <c r="O7" s="9"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="9"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="29">
+        <v>1028943852</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="21"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G8" s="1">
+        <f>(E8*0.35+F8*0.65)*0.1</f>
+        <v>0.26900000000000007</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I8" s="1">
+        <v>4</v>
+      </c>
+      <c r="J8" s="5">
+        <f>(AVERAGE(H8:I8)+N8)*0.4</f>
+        <v>2.08</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2.15</v>
+      </c>
+      <c r="L8" s="6">
+        <f>K8*0.5</f>
+        <v>1.075</v>
+      </c>
+      <c r="M8" s="6">
+        <v>8</v>
+      </c>
+      <c r="N8" s="6">
+        <f>M8/10</f>
+        <v>0.8</v>
+      </c>
+      <c r="O8" s="6">
+        <f>G8+J8+L8</f>
+        <v>3.4240000000000004</v>
+      </c>
+      <c r="P8" s="6">
+        <f>INT(O8*10)/10+IF(MOD(O8*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.4</v>
+      </c>
+      <c r="Q8" s="1" t="str">
+        <f>IF(O8&lt;3,3-O8,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="29">
+        <v>1013264286</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="31"/>
+      <c r="E9" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" ref="G9:G22" si="0">(E9*0.35+F9*0.65)*0.1</f>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" ref="J9:J22" si="1">(AVERAGE(H9:I9)+N9)*0.4</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <f t="shared" ref="L9:L22" si="2">K9*0.5</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="6">
+        <f t="shared" ref="N9:N22" si="3">M9/10</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <f>G9+J9+L9</f>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="P9" s="6">
+        <f>INT(O9*10)/10+IF(MOD(O9*10,1)&gt;=0.5,0.1,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="Q9" s="1">
+        <f>IF(O9&lt;3,3-O9,"No aplica")</f>
+        <v>2.8784999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="29">
+        <v>1013267876</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.2515</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="1"/>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3</v>
+      </c>
+      <c r="L10" s="6">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <f>G10+J10+L10</f>
+        <v>3.5115000000000003</v>
+      </c>
+      <c r="P10" s="6">
+        <f>INT(O10*10)/10+IF(MOD(O10*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="Q10" s="1" t="str">
+        <f>IF(O10&lt;3,3-O10,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="29">
+        <v>1014991121</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="31"/>
+      <c r="E11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.245</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="1"/>
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="18"/>
+      <c r="N11" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <f>G11+J11+L11</f>
+        <v>2.9450000000000003</v>
+      </c>
+      <c r="P11" s="6">
+        <f>INT(O11*10)/10+IF(MOD(O11*10,1)&gt;=0.5,0.1,0)</f>
+        <v>2.9</v>
+      </c>
+      <c r="Q11" s="1">
+        <f>IF(O11&lt;3,3-O11,"No aplica")</f>
+        <v>5.4999999999999716E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="29">
+        <v>1022961365</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="31"/>
+      <c r="E12" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.35350000000000004</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="1"/>
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" si="2"/>
+        <v>1.6</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <f>G12+J12+L12</f>
+        <v>3.8535000000000004</v>
+      </c>
+      <c r="P12" s="6">
+        <f>INT(O12*10)/10+IF(MOD(O12*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.9</v>
       </c>
-      <c r="F8" s="1">
+      <c r="Q12" s="1" t="str">
+        <f>IF(O12&lt;3,3-O12,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="29">
+        <v>1033714140</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="31"/>
+      <c r="E13" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.24750000000000003</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="1"/>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="K13" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" si="2"/>
+        <v>1.2</v>
+      </c>
+      <c r="M13" s="6">
+        <v>7</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="O13" s="6">
+        <f>G13+J13+L13</f>
+        <v>3.7275</v>
+      </c>
+      <c r="P13" s="6">
+        <f>INT(O13*10)/10+IF(MOD(O13*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.7</v>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <f>IF(O13&lt;3,3-O13,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="29">
+        <v>1013122283</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="31"/>
+      <c r="E14" s="1">
         <v>0.2</v>
       </c>
-      <c r="G8" s="1">
-        <f>(E8+F8)*0.1</f>
-        <v>0.41</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="F14" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.16950000000000001</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8800000000000001</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="2"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="6">
+        <f>G14+J14+L14</f>
+        <v>2.5994999999999999</v>
+      </c>
+      <c r="P14" s="6">
+        <f>INT(O14*10)/10+IF(MOD(O14*10,1)&gt;=0.5,0.1,0)</f>
+        <v>2.6</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>IF(O14&lt;3,3-O14,"No aplica")</f>
+        <v>0.40050000000000008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="29">
+        <v>1094051548</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.21850000000000003</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="M15" s="6">
+        <v>6</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="O15" s="6">
+        <f>G15+J15+L15</f>
+        <v>3.4584999999999999</v>
+      </c>
+      <c r="P15" s="6">
+        <f>INT(O15*10)/10+IF(MOD(O15*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="Q15" s="1" t="str">
+        <f>IF(O15&lt;3,3-O15,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="29">
+        <v>1031813370</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.32850000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1">
         <v>3.8</v>
       </c>
-      <c r="I8" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="J8" s="5">
-        <f t="shared" ref="J8:J22" si="0">AVERAGE(H8:I8)*0.4</f>
-        <v>1.6600000000000001</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="J16" s="5">
+        <f t="shared" si="1"/>
+        <v>1.56</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2.15</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="2"/>
+        <v>1.075</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
+        <f>G16+J16+L16</f>
+        <v>2.9634999999999998</v>
+      </c>
+      <c r="P16" s="6">
+        <f>INT(O16*10)/10+IF(MOD(O16*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>IF(O16&lt;3,3-O16,"No aplica")</f>
+        <v>3.6500000000000199E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="29">
+        <v>1034295843</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="31"/>
+      <c r="E17" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.33550000000000002</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="1"/>
+        <v>2.3200000000000003</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="2"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M17" s="6">
+        <v>9</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" si="3"/>
+        <v>0.9</v>
+      </c>
+      <c r="O17" s="6">
+        <f>G17+J17+L17</f>
+        <v>3.8055000000000003</v>
+      </c>
+      <c r="P17" s="6">
+        <f>INT(O17*10)/10+IF(MOD(O17*10,1)&gt;=0.5,0.1,0)</f>
         <v>3.8</v>
       </c>
-      <c r="L8" s="6">
-        <f t="shared" ref="L8:L22" si="1">K8*0.5</f>
-        <v>1.9</v>
-      </c>
-      <c r="M8" s="6">
-        <f t="shared" ref="M8:M22" si="2">G8+J8+L8</f>
-        <v>3.97</v>
-      </c>
-      <c r="N8" s="6">
-        <f t="shared" ref="N8:N22" si="3">INT(M8*10)/10+IF(MOD(M8*10,1)&gt;=0.5,0.1,0)</f>
+      <c r="Q17" s="1" t="str">
+        <f>IF(O17&lt;3,3-O17,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="29">
+        <v>1095551423</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="31"/>
+      <c r="E18" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="1"/>
+        <v>1.7600000000000002</v>
+      </c>
+      <c r="K18" s="1">
+        <v>3</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="6">
+        <f>G18+J18+L18</f>
+        <v>3.524</v>
+      </c>
+      <c r="P18" s="6">
+        <f>INT(O18*10)/10+IF(MOD(O18*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f>IF(O18&lt;3,3-O18,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="29">
+        <v>1087802193</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="31"/>
+      <c r="E19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="0"/>
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="1"/>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="M19" s="6">
+        <v>9</v>
+      </c>
+      <c r="N19" s="6">
+        <f t="shared" si="3"/>
+        <v>0.9</v>
+      </c>
+      <c r="O19" s="6">
+        <f>G19+J19+L19</f>
+        <v>3.7755000000000001</v>
+      </c>
+      <c r="P19" s="6">
+        <f>INT(O19*10)/10+IF(MOD(O19*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f>IF(O19&lt;3,3-O19,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="29">
+        <v>1072747164</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="31"/>
+      <c r="E20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="0"/>
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2800000000000002</v>
+      </c>
+      <c r="K20" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="2"/>
+        <v>1.625</v>
+      </c>
+      <c r="M20" s="6">
+        <v>7</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="O20" s="6">
+        <f>G20+J20+L20</f>
+        <v>3.1890000000000001</v>
+      </c>
+      <c r="P20" s="6">
+        <f>INT(O20*10)/10+IF(MOD(O20*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.2</v>
+      </c>
+      <c r="Q20" s="1" t="str">
+        <f>IF(O20&lt;3,3-O20,"No aplica")</f>
+        <v>No aplica</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="29">
+        <v>1075234817</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="31"/>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
         <v>4</v>
       </c>
-      <c r="O8" s="1" t="str">
-        <f t="shared" ref="O8:O22" si="4">IF(M8&lt;3,3-M8,"No aplica")</f>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="1">
-        <v>3.4</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" ref="G9:G22" si="5">(E9+F9)*0.1</f>
-        <v>0.34</v>
-      </c>
-      <c r="H9" s="1">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J9" s="5">
-        <f t="shared" si="0"/>
-        <v>1.4800000000000002</v>
-      </c>
-      <c r="K9" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="L9" s="6">
-        <f t="shared" si="1"/>
-        <v>1.125</v>
-      </c>
-      <c r="M9" s="6">
-        <f t="shared" si="2"/>
-        <v>2.9450000000000003</v>
-      </c>
-      <c r="N9" s="6">
-        <f t="shared" si="3"/>
-        <v>2.9</v>
-      </c>
-      <c r="O9" s="1">
-        <f t="shared" si="4"/>
-        <v>5.4999999999999716E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="5"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="H10" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I10" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="J10" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8600000000000003</v>
-      </c>
-      <c r="K10" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="L10" s="6">
-        <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-      <c r="M10" s="6">
-        <f t="shared" si="2"/>
-        <v>3.7600000000000002</v>
-      </c>
-      <c r="N10" s="6">
-        <f t="shared" si="3"/>
-        <v>3.8000000000000003</v>
-      </c>
-      <c r="O10" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="5"/>
-        <v>0.26</v>
-      </c>
-      <c r="H11" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I11" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8600000000000003</v>
-      </c>
-      <c r="K11" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="I21" s="1">
+        <v>5</v>
+      </c>
+      <c r="J21" s="5">
         <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="M11" s="6">
+      <c r="K21" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="L21" s="6">
         <f t="shared" si="2"/>
-        <v>3.92</v>
-      </c>
-      <c r="N11" s="6">
-        <f t="shared" si="3"/>
-        <v>3.9</v>
-      </c>
-      <c r="O11" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="5"/>
-        <v>0.38</v>
-      </c>
-      <c r="H12" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I12" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="J12" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8600000000000003</v>
-      </c>
-      <c r="K12" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="L12" s="6">
-        <f t="shared" si="1"/>
-        <v>1.8</v>
-      </c>
-      <c r="M12" s="6">
-        <f t="shared" si="2"/>
-        <v>4.04</v>
-      </c>
-      <c r="N12" s="6">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="O12" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="1">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="5"/>
-        <v>0.4</v>
-      </c>
-      <c r="H13" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="I13" s="1">
-        <v>5</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="0"/>
-        <v>1.94</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="L13" s="6">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="M13" s="6">
-        <f t="shared" si="2"/>
-        <v>3.84</v>
-      </c>
-      <c r="N13" s="6">
-        <f t="shared" si="3"/>
-        <v>3.8</v>
-      </c>
-      <c r="O13" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
-        <v>1016912717</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="1">
-        <v>5</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="1">
-        <v>5</v>
-      </c>
-      <c r="I14" s="1">
-        <v>5</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K14" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="L14" s="6">
-        <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M14" s="6">
-        <f t="shared" si="2"/>
-        <v>4.7</v>
-      </c>
-      <c r="N14" s="6">
-        <f t="shared" si="3"/>
-        <v>4.7</v>
-      </c>
-      <c r="O14" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="5"/>
-        <v>0.34000000000000008</v>
-      </c>
-      <c r="H15" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="I15" s="1">
-        <v>5</v>
-      </c>
-      <c r="J15" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9600000000000002</v>
-      </c>
-      <c r="K15" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="L15" s="6">
-        <f t="shared" si="1"/>
-        <v>1.8</v>
-      </c>
-      <c r="M15" s="6">
-        <f t="shared" si="2"/>
-        <v>4.1000000000000005</v>
-      </c>
-      <c r="N15" s="6">
-        <f t="shared" si="3"/>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="O15" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="1">
-        <v>2.9</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="5"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H16" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I16" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="0"/>
-        <v>1.88</v>
-      </c>
-      <c r="K16" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="L16" s="6">
-        <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-      <c r="M16" s="6">
-        <f t="shared" si="2"/>
-        <v>3.92</v>
-      </c>
-      <c r="N16" s="6">
-        <f t="shared" si="3"/>
-        <v>3.9</v>
-      </c>
-      <c r="O16" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="1">
-        <f t="shared" si="5"/>
-        <v>0.23000000000000004</v>
-      </c>
-      <c r="H17" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I17" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="J17" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8600000000000003</v>
-      </c>
-      <c r="K17" s="1">
-        <v>3</v>
-      </c>
-      <c r="L17" s="6">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="M17" s="6">
-        <f t="shared" si="2"/>
-        <v>3.5900000000000003</v>
-      </c>
-      <c r="N17" s="6">
-        <f t="shared" si="3"/>
-        <v>3.6</v>
-      </c>
-      <c r="O17" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G18" s="1">
-        <f t="shared" si="5"/>
-        <v>0.49000000000000005</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5</v>
-      </c>
-      <c r="I18" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J18" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9800000000000002</v>
-      </c>
-      <c r="K18" s="1">
-        <v>3.4</v>
-      </c>
-      <c r="L18" s="6">
-        <f t="shared" si="1"/>
-        <v>1.7</v>
-      </c>
-      <c r="M18" s="6">
-        <f t="shared" si="2"/>
-        <v>4.17</v>
-      </c>
-      <c r="N18" s="6">
-        <f t="shared" si="3"/>
-        <v>4.1999999999999993</v>
-      </c>
-      <c r="O18" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="5"/>
-        <v>0.05</v>
-      </c>
-      <c r="H19" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="I19" s="1">
-        <v>5</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="0"/>
-        <v>1.9600000000000002</v>
-      </c>
-      <c r="K19" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="L19" s="6">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="M19" s="6">
-        <f t="shared" si="2"/>
-        <v>2.6100000000000003</v>
-      </c>
-      <c r="N19" s="6">
-        <f t="shared" si="3"/>
-        <v>2.6</v>
-      </c>
-      <c r="O19" s="1">
-        <f t="shared" si="4"/>
-        <v>0.38999999999999968</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="5"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5</v>
-      </c>
-      <c r="I20" s="1">
-        <v>4.95</v>
-      </c>
-      <c r="J20" s="5">
-        <f t="shared" si="0"/>
-        <v>1.99</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L20" s="6">
-        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="M20" s="6">
-        <f t="shared" si="2"/>
-        <v>3.19</v>
-      </c>
-      <c r="N20" s="6">
-        <f t="shared" si="3"/>
-        <v>3.2</v>
-      </c>
-      <c r="O20" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="5"/>
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="H21" s="1">
-        <v>4</v>
-      </c>
-      <c r="I21" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="J21" s="5">
-        <f t="shared" si="0"/>
-        <v>1.74</v>
-      </c>
-      <c r="K21" s="1">
-        <v>2.9</v>
-      </c>
-      <c r="L21" s="6">
-        <f t="shared" si="1"/>
-        <v>1.45</v>
-      </c>
-      <c r="M21" s="6">
-        <f t="shared" si="2"/>
-        <v>3.54</v>
-      </c>
+      <c r="M21" s="6"/>
       <c r="N21" s="6">
         <f t="shared" si="3"/>
-        <v>3.5</v>
-      </c>
-      <c r="O21" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="6">
+        <f>G21+J21+L21</f>
+        <v>2.7</v>
+      </c>
+      <c r="P21" s="6">
+        <f>INT(O21*10)/10+IF(MOD(O21*10,1)&gt;=0.5,0.1,0)</f>
+        <v>2.7</v>
+      </c>
+      <c r="Q21" s="1">
+        <f>IF(O21&lt;3,3-O21,"No aplica")</f>
+        <v>0.29999999999999982</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="29">
+        <v>1016912717</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="31"/>
       <c r="E22" s="1">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="1">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="5"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="0"/>
+        <v>0.10200000000000001</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
       </c>
       <c r="I22" s="1">
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8</v>
+        <f t="shared" si="1"/>
+        <v>1.92</v>
       </c>
       <c r="K22" s="1">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="1"/>
-        <v>1.6</v>
-      </c>
-      <c r="M22" s="6">
         <f t="shared" si="2"/>
-        <v>3.68</v>
-      </c>
+        <v>1.875</v>
+      </c>
+      <c r="M22" s="6"/>
       <c r="N22" s="6">
         <f t="shared" si="3"/>
-        <v>3.7</v>
-      </c>
-      <c r="O22" s="1" t="str">
-        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="6">
+        <f>G22+J22+L22</f>
+        <v>3.8969999999999998</v>
+      </c>
+      <c r="P22" s="6">
+        <f>INT(O22*10)/10+IF(MOD(O22*10,1)&gt;=0.5,0.1,0)</f>
+        <v>3.9</v>
+      </c>
+      <c r="Q22" s="1" t="str">
+        <f>IF(O22&lt;3,3-O22,"No aplica")</f>
         <v>No aplica</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O7" xr:uid="{FEA64364-85F1-4B4C-B1BB-0179859BFB61}">
-    <filterColumn colId="0" showButton="0"/>
-    <filterColumn colId="2" showButton="0"/>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:O22">
-      <sortCondition ref="C7"/>
-    </sortState>
-  </autoFilter>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A21:B21"/>
@@ -4294,6 +5510,7 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A2:B2"/>
@@ -4301,1098 +5518,62 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:I3"/>
   </mergeCells>
+  <conditionalFormatting sqref="H8:I21">
+    <cfRule type="expression" dxfId="11" priority="18">
+      <formula>H8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:I21">
+    <cfRule type="expression" dxfId="10" priority="17">
+      <formula>H8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:K22">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>K8&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:K22">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>K8&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22">
+    <cfRule type="expression" dxfId="7" priority="10">
+      <formula>H22&lt;3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>H22&gt;=3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E8:F22">
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>E8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>E8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:I22">
-    <cfRule type="expression" dxfId="15" priority="5">
-      <formula>H8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="6">
-      <formula>H8&lt;3</formula>
+  <conditionalFormatting sqref="E8:F22">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>E8&gt;=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K22">
-    <cfRule type="expression" dxfId="13" priority="9">
-      <formula>K8&gt;=3</formula>
+  <conditionalFormatting sqref="O8:O22">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>O8&lt;3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10">
-      <formula>K8&lt;3</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O8:O22">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>O8&gt;=3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:M22">
-    <cfRule type="expression" dxfId="11" priority="7">
-      <formula>M8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8">
-      <formula>M8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D02CB94-BE69-462D-965B-A4EABD13502C}">
-  <dimension ref="A1:Q22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" customWidth="1"/>
-    <col min="13" max="13" width="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="9"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
-        <v>1028943852</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="G8" s="1">
-        <f>(E8*0.35+F8*0.65)*0.1</f>
-        <v>0.26900000000000007</v>
-      </c>
-      <c r="H8" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="I8" s="1">
-        <v>4</v>
-      </c>
-      <c r="J8" s="5">
-        <f>(AVERAGE(H8:I8)+N8)*0.4</f>
-        <v>2.08</v>
-      </c>
-      <c r="K8" s="1">
-        <v>2.15</v>
-      </c>
-      <c r="L8" s="6">
-        <f>K8*0.5</f>
-        <v>1.075</v>
-      </c>
-      <c r="M8" s="6">
-        <v>8</v>
-      </c>
-      <c r="N8" s="6">
-        <f>M8/10</f>
-        <v>0.8</v>
-      </c>
-      <c r="O8" s="6">
-        <f t="shared" ref="O8:O22" si="0">G8+J8+L8</f>
-        <v>3.4240000000000004</v>
-      </c>
-      <c r="P8" s="6">
-        <f t="shared" ref="P8:P22" si="1">INT(O8*10)/10+IF(MOD(O8*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.4</v>
-      </c>
-      <c r="Q8" s="1" t="str">
-        <f t="shared" ref="Q8:Q22" si="2">IF(O8&lt;3,3-O8,"No aplica")</f>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
-        <v>1013264286</v>
-      </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" ref="G9:G22" si="3">(E9*0.35+F9*0.65)*0.1</f>
-        <v>0.12150000000000001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <f t="shared" ref="J9:J22" si="4">(AVERAGE(H9:I9)+N9)*0.4</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <f t="shared" ref="L9:L22" si="5">K9*0.5</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="6">
-        <f t="shared" ref="N9:N22" si="6">M9/10</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="6">
-        <f t="shared" si="0"/>
-        <v>0.12150000000000001</v>
-      </c>
-      <c r="P9" s="6">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="Q9" s="1">
-        <f t="shared" si="2"/>
-        <v>2.8784999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
-        <v>1013267876</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="3"/>
-        <v>0.2515</v>
-      </c>
-      <c r="H10" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I10" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="J10" s="5">
-        <f t="shared" si="4"/>
-        <v>1.7600000000000002</v>
-      </c>
-      <c r="K10" s="1">
-        <v>3</v>
-      </c>
-      <c r="L10" s="6">
-        <f t="shared" si="5"/>
-        <v>1.5</v>
-      </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="6">
-        <f t="shared" si="0"/>
-        <v>3.5115000000000003</v>
-      </c>
-      <c r="P10" s="6">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="Q10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
-        <v>1014991121</v>
-      </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="3"/>
-        <v>0.245</v>
-      </c>
-      <c r="H11" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="I11" s="1">
-        <v>5</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" si="4"/>
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="K11" s="1">
-        <v>2</v>
-      </c>
-      <c r="L11" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="18"/>
-      <c r="N11" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="6">
-        <f t="shared" si="0"/>
-        <v>2.9450000000000003</v>
-      </c>
-      <c r="P11" s="6">
-        <f t="shared" si="1"/>
-        <v>2.9</v>
-      </c>
-      <c r="Q11" s="1">
-        <f t="shared" si="2"/>
-        <v>5.4999999999999716E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
-        <v>1022961365</v>
-      </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="1">
-        <v>3.6</v>
-      </c>
-      <c r="F12" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="3"/>
-        <v>0.35350000000000004</v>
-      </c>
-      <c r="H12" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I12" s="1">
-        <v>5</v>
-      </c>
-      <c r="J12" s="5">
-        <f t="shared" si="4"/>
-        <v>1.9000000000000001</v>
-      </c>
-      <c r="K12" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="L12" s="6">
-        <f t="shared" si="5"/>
-        <v>1.6</v>
-      </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" si="0"/>
-        <v>3.8535000000000004</v>
-      </c>
-      <c r="P12" s="6">
-        <f t="shared" si="1"/>
-        <v>3.9</v>
-      </c>
-      <c r="Q12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
-        <v>1033714140</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="F13" s="1">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="3"/>
-        <v>0.24750000000000003</v>
-      </c>
-      <c r="H13" s="1">
-        <v>5</v>
-      </c>
-      <c r="I13" s="1">
-        <v>5</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="K13" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="L13" s="6">
-        <f t="shared" si="5"/>
-        <v>1.2</v>
-      </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="6">
-        <f t="shared" si="0"/>
-        <v>3.4474999999999998</v>
-      </c>
-      <c r="P13" s="6">
-        <f t="shared" si="1"/>
-        <v>3.4</v>
-      </c>
-      <c r="Q13" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
-        <v>1013122283</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="G14" s="1">
-        <f t="shared" si="3"/>
-        <v>0.16950000000000001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I14" s="1">
-        <v>5</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="4"/>
-        <v>1.8800000000000001</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L14" s="6">
-        <f t="shared" si="5"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="6">
-        <f t="shared" si="0"/>
-        <v>2.5994999999999999</v>
-      </c>
-      <c r="P14" s="6">
-        <f t="shared" si="1"/>
-        <v>2.6</v>
-      </c>
-      <c r="Q14" s="1">
-        <f t="shared" si="2"/>
-        <v>0.40050000000000008</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <v>1094051548</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F15" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="3"/>
-        <v>0.21850000000000003</v>
-      </c>
-      <c r="H15" s="1">
-        <v>3</v>
-      </c>
-      <c r="I15" s="1">
-        <v>5</v>
-      </c>
-      <c r="J15" s="5">
-        <f t="shared" si="4"/>
-        <v>1.8399999999999999</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="L15" s="6">
-        <f t="shared" si="5"/>
-        <v>1.4</v>
-      </c>
-      <c r="M15" s="6">
-        <v>6</v>
-      </c>
-      <c r="N15" s="6">
-        <f t="shared" si="6"/>
-        <v>0.6</v>
-      </c>
-      <c r="O15" s="6">
-        <f t="shared" si="0"/>
-        <v>3.4584999999999999</v>
-      </c>
-      <c r="P15" s="6">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="Q15" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
-        <v>1031813370</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="F16" s="1">
-        <v>4.3</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="3"/>
-        <v>0.32850000000000001</v>
-      </c>
-      <c r="H16" s="1">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="4"/>
-        <v>1.56</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2.15</v>
-      </c>
-      <c r="L16" s="6">
-        <f t="shared" si="5"/>
-        <v>1.075</v>
-      </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="6">
-        <f t="shared" si="0"/>
-        <v>2.9634999999999998</v>
-      </c>
-      <c r="P16" s="6">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="Q16" s="1">
-        <f t="shared" si="2"/>
-        <v>3.6500000000000199E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
-        <v>1034295843</v>
-      </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="F17" s="1">
-        <v>4.3</v>
-      </c>
-      <c r="G17" s="1">
-        <f t="shared" si="3"/>
-        <v>0.33550000000000002</v>
-      </c>
-      <c r="H17" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="I17" s="1">
-        <v>5</v>
-      </c>
-      <c r="J17" s="5">
-        <f t="shared" si="4"/>
-        <v>2.3200000000000003</v>
-      </c>
-      <c r="K17" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="L17" s="6">
-        <f t="shared" si="5"/>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="M17" s="6">
-        <v>9</v>
-      </c>
-      <c r="N17" s="6">
-        <f t="shared" si="6"/>
-        <v>0.9</v>
-      </c>
-      <c r="O17" s="6">
-        <f t="shared" si="0"/>
-        <v>3.8055000000000003</v>
-      </c>
-      <c r="P17" s="6">
-        <f t="shared" si="1"/>
-        <v>3.8</v>
-      </c>
-      <c r="Q17" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
-        <v>1095551423</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F18" s="1">
-        <v>3.9</v>
-      </c>
-      <c r="G18" s="1">
-        <f t="shared" si="3"/>
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5</v>
-      </c>
-      <c r="I18" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="J18" s="5">
-        <f t="shared" si="4"/>
-        <v>1.7600000000000002</v>
-      </c>
-      <c r="K18" s="1">
-        <v>3</v>
-      </c>
-      <c r="L18" s="6">
-        <f t="shared" si="5"/>
-        <v>1.5</v>
-      </c>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="6">
-        <f t="shared" si="0"/>
-        <v>3.524</v>
-      </c>
-      <c r="P18" s="6">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="Q18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
-        <v>1087802193</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="3"/>
-        <v>0.22550000000000001</v>
-      </c>
-      <c r="H19" s="1">
-        <v>5</v>
-      </c>
-      <c r="I19" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="J19" s="5">
-        <f t="shared" si="4"/>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="K19" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="L19" s="6">
-        <f t="shared" si="5"/>
-        <v>1.25</v>
-      </c>
-      <c r="M19" s="6">
-        <v>9</v>
-      </c>
-      <c r="N19" s="6">
-        <f t="shared" si="6"/>
-        <v>0.9</v>
-      </c>
-      <c r="O19" s="6">
-        <f t="shared" si="0"/>
-        <v>3.7755000000000001</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="1"/>
-        <v>3.8000000000000003</v>
-      </c>
-      <c r="Q19" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
-        <v>1072747164</v>
-      </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="3"/>
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5">
-        <f t="shared" si="4"/>
-        <v>1.2800000000000002</v>
-      </c>
-      <c r="K20" s="1">
-        <v>3.25</v>
-      </c>
-      <c r="L20" s="6">
-        <f t="shared" si="5"/>
-        <v>1.625</v>
-      </c>
-      <c r="M20" s="6">
-        <v>7</v>
-      </c>
-      <c r="N20" s="6">
-        <f t="shared" si="6"/>
-        <v>0.7</v>
-      </c>
-      <c r="O20" s="6">
-        <f t="shared" si="0"/>
-        <v>3.1890000000000001</v>
-      </c>
-      <c r="P20" s="6">
-        <f t="shared" si="1"/>
-        <v>3.2</v>
-      </c>
-      <c r="Q20" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
-        <v>1075234817</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>4</v>
-      </c>
-      <c r="I21" s="1">
-        <v>5</v>
-      </c>
-      <c r="J21" s="5">
-        <f t="shared" si="4"/>
-        <v>1.8</v>
-      </c>
-      <c r="K21" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L21" s="6">
-        <f t="shared" si="5"/>
-        <v>0.9</v>
-      </c>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="6">
-        <f t="shared" si="0"/>
-        <v>2.7</v>
-      </c>
-      <c r="P21" s="6">
-        <f t="shared" si="1"/>
-        <v>2.7</v>
-      </c>
-      <c r="Q21" s="1">
-        <f t="shared" si="2"/>
-        <v>0.29999999999999982</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
-        <v>1016912717</v>
-      </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="G22" s="1">
-        <f t="shared" si="3"/>
-        <v>0.10200000000000001</v>
-      </c>
-      <c r="H22" s="1">
-        <v>5</v>
-      </c>
-      <c r="I22" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J22" s="5">
-        <f t="shared" si="4"/>
-        <v>1.92</v>
-      </c>
-      <c r="K22" s="1">
-        <v>3.75</v>
-      </c>
-      <c r="L22" s="6">
-        <f t="shared" si="5"/>
-        <v>1.875</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="6">
-        <f t="shared" si="0"/>
-        <v>3.8969999999999998</v>
-      </c>
-      <c r="P22" s="6">
-        <f t="shared" si="1"/>
-        <v>3.9</v>
-      </c>
-      <c r="Q22" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>No aplica</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E8:F22">
-    <cfRule type="expression" dxfId="9" priority="5">
-      <formula>E8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
-      <formula>E8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:I22">
-    <cfRule type="expression" dxfId="7" priority="9">
-      <formula>H8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="10">
-      <formula>H8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8:K22">
-    <cfRule type="expression" dxfId="5" priority="15">
-      <formula>K8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="16">
-      <formula>K8&lt;3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M8:M22">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="2" priority="2">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
       <formula>LEN(TRIM(M8))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O22">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>O8&gt;=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>O8&lt;3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Corte_3.xlsx
+++ b/Corte_3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="994" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75DC8D28-CAE7-4731-98F5-BBA64923177B}"/>
+  <xr:revisionPtr revIDLastSave="997" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{377AC60A-551E-4F7D-AB54-C6AEC8BE23F1}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4503,7 +4503,7 @@
   <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" customWidth="1"/>
     <col min="9" max="9" width="16.5703125" customWidth="1"/>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="K21" s="1">
         <v>1.8</v>
@@ -5400,22 +5400,24 @@
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
-      <c r="M21" s="6"/>
+      <c r="M21" s="6">
+        <v>3</v>
+      </c>
       <c r="N21" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O21" s="6">
         <f>G21+J21+L21</f>
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="P21" s="6">
         <f>INT(O21*10)/10+IF(MOD(O21*10,1)&gt;=0.5,0.1,0)</f>
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" s="1">
         <f>IF(O21&lt;3,3-O21,"No aplica")</f>
-        <v>0.29999999999999982</v>
+        <v>0.18000000000000016</v>
       </c>
     </row>
     <row r="22" spans="1:17">

--- a/Corte_3.xlsx
+++ b/Corte_3.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="997" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{377AC60A-551E-4F7D-AB54-C6AEC8BE23F1}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="11_7E4E55BF84DCCEE3ED7FF6F99031F45BFA722949" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B069EC90-7D76-4B78-9EE0-F1C642261302}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Corte!$A$7:$X$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Corte 1'!$A$7:$P$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Corte 2'!$A$7:$O$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Corte 3'!$A$7:$Q$7</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -454,22 +455,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -484,14 +482,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -501,9 +505,6 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1348,55 +1349,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="35"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
@@ -1405,43 +1406,43 @@
       <c r="U3" s="13"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="14">
         <v>0.1</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
       <c r="M6" s="3">
         <v>0.4</v>
       </c>
@@ -1451,13 +1452,13 @@
       <c r="O6" s="4">
         <v>0.5</v>
       </c>
-      <c r="P6" s="32" t="s">
+      <c r="P6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="35"/>
       <c r="U6" s="12" t="s">
         <v>13</v>
       </c>
@@ -1472,14 +1473,14 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -1524,14 +1525,14 @@
       <c r="X7" s="9"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="31"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
         <f>E8*0.1</f>
@@ -1575,14 +1576,14 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
         <f t="shared" ref="F9:F22" si="2">E9*0.1</f>
@@ -1626,14 +1627,14 @@
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
         <f t="shared" si="2"/>
@@ -1677,14 +1678,14 @@
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="31"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
         <f t="shared" si="2"/>
@@ -1728,14 +1729,14 @@
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="31"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
         <f t="shared" si="2"/>
@@ -1780,14 +1781,14 @@
       <c r="AA12" s="8"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
         <f t="shared" si="2"/>
@@ -1831,14 +1832,14 @@
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1">
         <f t="shared" si="2"/>
@@ -1882,14 +1883,14 @@
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1">
         <f t="shared" si="2"/>
@@ -1933,14 +1934,14 @@
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
         <f t="shared" si="2"/>
@@ -1984,14 +1985,14 @@
       </c>
     </row>
     <row r="17" spans="1:24">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="31"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
         <f t="shared" si="2"/>
@@ -2035,14 +2036,14 @@
       </c>
     </row>
     <row r="18" spans="1:24">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="31"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1">
         <f t="shared" si="2"/>
@@ -2086,14 +2087,14 @@
       </c>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1">
         <f t="shared" si="2"/>
@@ -2137,14 +2138,14 @@
       </c>
     </row>
     <row r="20" spans="1:24">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1">
         <f t="shared" si="2"/>
@@ -2188,14 +2189,14 @@
       </c>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="31"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1">
         <f t="shared" si="2"/>
@@ -2239,14 +2240,14 @@
       </c>
     </row>
     <row r="22" spans="1:24">
-      <c r="A22" s="29">
+      <c r="A22" s="19">
         <v>1016912717</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="31"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1">
         <f t="shared" si="2"/>
@@ -2295,6 +2296,33 @@
     <filterColumn colId="2" showButton="0"/>
   </autoFilter>
   <mergeCells count="43">
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A11:B11"/>
@@ -2311,33 +2339,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:L21">
     <cfRule type="expression" dxfId="47" priority="14">
@@ -2431,24 +2432,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="36" t="s">
         <v>3</v>
       </c>
@@ -2459,24 +2460,24 @@
       <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="37"/>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="19"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="38" t="s">
         <v>7</v>
       </c>
@@ -2487,22 +2488,22 @@
       <c r="H4" s="38"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="14">
         <v>0.1</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="3">
         <v>0.4</v>
       </c>
@@ -2532,14 +2533,14 @@
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -2561,14 +2562,14 @@
       <c r="Q7" s="9"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="31"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="1">
         <v>5</v>
       </c>
@@ -2616,14 +2617,14 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="1">
         <v>5</v>
       </c>
@@ -2673,14 +2674,14 @@
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="1">
         <v>3.5</v>
       </c>
@@ -2728,14 +2729,14 @@
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="31"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="1">
         <v>3.1</v>
       </c>
@@ -2785,14 +2786,14 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="31"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="1">
         <v>3.4</v>
       </c>
@@ -2842,14 +2843,14 @@
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="1">
         <v>3.5</v>
       </c>
@@ -2899,14 +2900,14 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="29">
+      <c r="A14" s="19">
         <v>1016912717</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="1">
         <v>2.8</v>
       </c>
@@ -2956,14 +2957,14 @@
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="1">
         <v>3.7</v>
       </c>
@@ -3013,14 +3014,14 @@
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="1">
         <v>2</v>
       </c>
@@ -3070,14 +3071,14 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="31"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="1">
         <v>3.4</v>
       </c>
@@ -3127,14 +3128,14 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="31"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="1">
         <v>3.2</v>
       </c>
@@ -3184,14 +3185,14 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="1">
         <v>1.8</v>
       </c>
@@ -3239,14 +3240,14 @@
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="1">
         <v>2.6</v>
       </c>
@@ -3296,14 +3297,14 @@
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="31"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="1">
         <v>3.9</v>
       </c>
@@ -3351,14 +3352,14 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="31"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="1">
         <v>2.5</v>
       </c>
@@ -3414,36 +3415,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="42">
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A1:B1"/>
@@ -3456,6 +3427,36 @@
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:H21">
     <cfRule type="expression" dxfId="33" priority="16">
@@ -3534,25 +3535,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="22"/>
       <c r="C2" s="36" t="s">
         <v>3</v>
       </c>
@@ -3564,25 +3565,25 @@
       <c r="I2" s="36"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="37"/>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="19"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="38" t="s">
         <v>7</v>
       </c>
@@ -3594,12 +3595,12 @@
       <c r="I4" s="38"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
@@ -3609,10 +3610,10 @@
       <c r="G6" s="14">
         <v>0.1</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="25"/>
+      <c r="I6" s="24"/>
       <c r="J6" s="3">
         <v>0.4</v>
       </c>
@@ -3633,14 +3634,14 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -3658,14 +3659,14 @@
       <c r="O7" s="9"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="31"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="1">
         <v>3.9</v>
       </c>
@@ -3707,14 +3708,14 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="1">
         <v>3.4</v>
       </c>
@@ -3756,14 +3757,14 @@
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="1">
         <v>1.3</v>
       </c>
@@ -3805,14 +3806,14 @@
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="31"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="1">
         <v>2.6</v>
       </c>
@@ -3854,14 +3855,14 @@
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="31"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="1">
         <v>3.8</v>
       </c>
@@ -3903,14 +3904,14 @@
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="1">
         <v>4</v>
       </c>
@@ -3952,14 +3953,14 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="29">
+      <c r="A14" s="19">
         <v>1016912717</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="31"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="1">
         <v>5</v>
       </c>
@@ -4001,14 +4002,14 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="31"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="1">
         <v>3.2</v>
       </c>
@@ -4050,14 +4051,14 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="31"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="1">
         <v>2.9</v>
       </c>
@@ -4099,14 +4100,14 @@
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="31"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="1">
         <v>2.1</v>
       </c>
@@ -4148,14 +4149,14 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="31"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="1">
         <v>4.7</v>
       </c>
@@ -4197,14 +4198,14 @@
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="21"/>
       <c r="E19" s="1">
         <v>0.5</v>
       </c>
@@ -4246,14 +4247,14 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="21"/>
       <c r="E20" s="1">
         <v>2.8</v>
       </c>
@@ -4295,14 +4296,14 @@
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="31"/>
+      <c r="D21" s="21"/>
       <c r="E21" s="1">
         <v>3.5</v>
       </c>
@@ -4344,14 +4345,14 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="31"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="1">
         <v>2.6</v>
       </c>
@@ -4401,48 +4402,48 @@
     </sortState>
   </autoFilter>
   <mergeCells count="42">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <conditionalFormatting sqref="H8:I21">
     <cfRule type="expression" dxfId="21" priority="12">
@@ -4503,7 +4504,7 @@
   <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" customWidth="1"/>
     <col min="9" max="9" width="16.5703125" customWidth="1"/>
@@ -4515,83 +4516,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="27" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="28"/>
+      <c r="F6" s="27"/>
       <c r="G6" s="14">
         <v>0.1</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="25"/>
+      <c r="I6" s="24"/>
       <c r="J6" s="3">
         <v>0.4</v>
       </c>
@@ -4618,14 +4619,14 @@
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="9" t="s">
         <v>60</v>
       </c>
@@ -4651,14 +4652,14 @@
       <c r="Q7" s="9"/>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="29">
+      <c r="A8" s="19">
         <v>1028943852</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="31"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="1">
         <v>1</v>
       </c>
@@ -4707,14 +4708,14 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="29">
+      <c r="A9" s="19">
         <v>1013264286</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="1">
         <v>0.5</v>
       </c>
@@ -4722,7 +4723,7 @@
         <v>1.6</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" ref="G9:G22" si="0">(E9*0.35+F9*0.65)*0.1</f>
+        <f>(E9*0.35+F9*0.65)*0.1</f>
         <v>0.12150000000000001</v>
       </c>
       <c r="H9" s="1">
@@ -4732,19 +4733,19 @@
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J22" si="1">(AVERAGE(H9:I9)+N9)*0.4</f>
+        <f>(AVERAGE(H9:I9)+N9)*0.4</f>
         <v>0</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" ref="L9:L22" si="2">K9*0.5</f>
+        <f>K9*0.5</f>
         <v>0</v>
       </c>
       <c r="M9" s="17"/>
       <c r="N9" s="6">
-        <f t="shared" ref="N9:N22" si="3">M9/10</f>
+        <f>M9/10</f>
         <v>0</v>
       </c>
       <c r="O9" s="6">
@@ -4761,14 +4762,14 @@
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="29">
+      <c r="A10" s="19">
         <v>1013267876</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="1">
         <v>0.5</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v>3.6</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="0"/>
+        <f>(E10*0.35+F10*0.65)*0.1</f>
         <v>0.2515</v>
       </c>
       <c r="H10" s="1">
@@ -4786,19 +4787,19 @@
         <v>4.2</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="1"/>
+        <f>(AVERAGE(H10:I10)+N10)*0.4</f>
         <v>1.7600000000000002</v>
       </c>
       <c r="K10" s="1">
         <v>3</v>
       </c>
       <c r="L10" s="6">
-        <f t="shared" si="2"/>
+        <f>K10*0.5</f>
         <v>1.5</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="16">
-        <f t="shared" si="3"/>
+        <f>M10/10</f>
         <v>0</v>
       </c>
       <c r="O10" s="6">
@@ -4815,14 +4816,14 @@
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="29">
+      <c r="A11" s="19">
         <v>1014991121</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="31"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="1">
         <v>0.5</v>
       </c>
@@ -4830,7 +4831,7 @@
         <v>3.5</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
+        <f>(E11*0.35+F11*0.65)*0.1</f>
         <v>0.245</v>
       </c>
       <c r="H11" s="1">
@@ -4840,19 +4841,19 @@
         <v>5</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="1"/>
+        <f>(AVERAGE(H11:I11)+N11)*0.4</f>
         <v>1.7000000000000002</v>
       </c>
       <c r="K11" s="1">
         <v>2</v>
       </c>
       <c r="L11" s="6">
-        <f t="shared" si="2"/>
+        <f>K11*0.5</f>
         <v>1</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="6">
-        <f t="shared" si="3"/>
+        <f>M11/10</f>
         <v>0</v>
       </c>
       <c r="O11" s="6">
@@ -4869,14 +4870,14 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="29">
+      <c r="A12" s="19">
         <v>1022961365</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="31"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="1">
         <v>3.6</v>
       </c>
@@ -4884,7 +4885,7 @@
         <v>3.5</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="0"/>
+        <f>(E12*0.35+F12*0.65)*0.1</f>
         <v>0.35350000000000004</v>
       </c>
       <c r="H12" s="1">
@@ -4894,19 +4895,19 @@
         <v>5</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="1"/>
+        <f>(AVERAGE(H12:I12)+N12)*0.4</f>
         <v>1.9000000000000001</v>
       </c>
       <c r="K12" s="1">
         <v>3.2</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="2"/>
+        <f>K12*0.5</f>
         <v>1.6</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="6">
-        <f t="shared" si="3"/>
+        <f>M12/10</f>
         <v>0</v>
       </c>
       <c r="O12" s="6">
@@ -4923,14 +4924,14 @@
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="29">
+      <c r="A13" s="19">
         <v>1033714140</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="31"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="1">
         <v>1.5</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="0"/>
+        <f>(E13*0.35+F13*0.65)*0.1</f>
         <v>0.24750000000000003</v>
       </c>
       <c r="H13" s="1">
@@ -4948,21 +4949,21 @@
         <v>5</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="1"/>
+        <f>(AVERAGE(H13:I13)+N13)*0.4</f>
         <v>2.2800000000000002</v>
       </c>
       <c r="K13" s="1">
         <v>2.4</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="2"/>
+        <f>K13*0.5</f>
         <v>1.2</v>
       </c>
       <c r="M13" s="6">
         <v>7</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="3"/>
+        <f>M13/10</f>
         <v>0.7</v>
       </c>
       <c r="O13" s="6">
@@ -4979,273 +4980,273 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="29">
-        <v>1013122283</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="31"/>
+      <c r="A14" s="19">
+        <v>1016912717</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="1">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F14" s="1">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="0"/>
-        <v>0.16950000000000001</v>
+        <f>(E14*0.35+F14*0.65)*0.1</f>
+        <v>0.10200000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I14" s="1">
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J14" s="5">
-        <f t="shared" si="1"/>
-        <v>1.8800000000000001</v>
+        <f>(AVERAGE(H14:I14)+N14)*0.4</f>
+        <v>1.92</v>
       </c>
       <c r="K14" s="1">
-        <v>1.1000000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="2"/>
-        <v>0.55000000000000004</v>
+        <f>K14*0.5</f>
+        <v>1.875</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6">
-        <f t="shared" si="3"/>
+        <f>M14/10</f>
         <v>0</v>
       </c>
       <c r="O14" s="6">
         <f>G14+J14+L14</f>
-        <v>2.5994999999999999</v>
+        <v>3.8969999999999998</v>
       </c>
       <c r="P14" s="6">
         <f>INT(O14*10)/10+IF(MOD(O14*10,1)&gt;=0.5,0.1,0)</f>
-        <v>2.6</v>
-      </c>
-      <c r="Q14" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="Q14" s="1" t="str">
         <f>IF(O14&lt;3,3-O14,"No aplica")</f>
-        <v>0.40050000000000008</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="29">
-        <v>1094051548</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="31"/>
+      <c r="A15" s="19">
+        <v>1013122283</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="21"/>
       <c r="E15" s="1">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="1">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="0"/>
-        <v>0.21850000000000003</v>
+        <f>(E15*0.35+F15*0.65)*0.1</f>
+        <v>0.16950000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I15" s="1">
         <v>5</v>
       </c>
       <c r="J15" s="5">
-        <f t="shared" si="1"/>
-        <v>1.8399999999999999</v>
+        <f>(AVERAGE(H15:I15)+N15)*0.4</f>
+        <v>1.8800000000000001</v>
       </c>
       <c r="K15" s="1">
-        <v>2.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="2"/>
-        <v>1.4</v>
-      </c>
-      <c r="M15" s="6">
-        <v>6</v>
-      </c>
+        <f>K15*0.5</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M15" s="6"/>
       <c r="N15" s="6">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
+        <f>M15/10</f>
+        <v>0</v>
       </c>
       <c r="O15" s="6">
         <f>G15+J15+L15</f>
-        <v>3.4584999999999999</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="P15" s="6">
         <f>INT(O15*10)/10+IF(MOD(O15*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="Q15" s="1" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="Q15" s="1">
         <f>IF(O15&lt;3,3-O15,"No aplica")</f>
-        <v>No aplica</v>
+        <v>0.40050000000000008</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="29">
-        <v>1031813370</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="31"/>
+      <c r="A16" s="19">
+        <v>1094051548</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="21"/>
       <c r="E16" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="G16" s="1">
+        <f>(E16*0.35+F16*0.65)*0.1</f>
+        <v>0.21850000000000003</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>5</v>
+      </c>
+      <c r="J16" s="5">
+        <f>(AVERAGE(H16:I16)+N16)*0.4</f>
+        <v>1.8399999999999999</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="L16" s="6">
+        <f>K16*0.5</f>
         <v>1.4</v>
       </c>
-      <c r="F16" s="1">
-        <v>4.3</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="0"/>
-        <v>0.32850000000000001</v>
-      </c>
-      <c r="H16" s="1">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="J16" s="5">
-        <f t="shared" si="1"/>
-        <v>1.56</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2.15</v>
-      </c>
-      <c r="L16" s="6">
-        <f t="shared" si="2"/>
-        <v>1.075</v>
-      </c>
-      <c r="M16" s="6"/>
+      <c r="M16" s="6">
+        <v>6</v>
+      </c>
       <c r="N16" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>M16/10</f>
+        <v>0.6</v>
       </c>
       <c r="O16" s="6">
         <f>G16+J16+L16</f>
-        <v>2.9634999999999998</v>
+        <v>3.4584999999999999</v>
       </c>
       <c r="P16" s="6">
         <f>INT(O16*10)/10+IF(MOD(O16*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3</v>
-      </c>
-      <c r="Q16" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="Q16" s="1" t="str">
         <f>IF(O16&lt;3,3-O16,"No aplica")</f>
-        <v>3.6500000000000199E-2</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="29">
-        <v>1034295843</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="31"/>
+      <c r="A17" s="19">
+        <v>1031813370</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="21"/>
       <c r="E17" s="1">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F17" s="1">
         <v>4.3</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="0"/>
-        <v>0.33550000000000002</v>
+        <f>(E17*0.35+F17*0.65)*0.1</f>
+        <v>0.32850000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="1"/>
-        <v>2.3200000000000003</v>
+        <f>(AVERAGE(H17:I17)+N17)*0.4</f>
+        <v>1.56</v>
       </c>
       <c r="K17" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.15</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="2"/>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="M17" s="6">
-        <v>9</v>
-      </c>
+        <f>K17*0.5</f>
+        <v>1.075</v>
+      </c>
+      <c r="M17" s="6"/>
       <c r="N17" s="6">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>M17/10</f>
+        <v>0</v>
       </c>
       <c r="O17" s="6">
         <f>G17+J17+L17</f>
-        <v>3.8055000000000003</v>
+        <v>2.9634999999999998</v>
       </c>
       <c r="P17" s="6">
         <f>INT(O17*10)/10+IF(MOD(O17*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.8</v>
-      </c>
-      <c r="Q17" s="1" t="str">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="1">
         <f>IF(O17&lt;3,3-O17,"No aplica")</f>
-        <v>No aplica</v>
+        <v>3.6500000000000199E-2</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="29">
-        <v>1095551423</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="31"/>
+      <c r="A18" s="19">
+        <v>1034295843</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="1">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="F18" s="1">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="0"/>
-        <v>0.26400000000000001</v>
+        <f>(E18*0.35+F18*0.65)*0.1</f>
+        <v>0.33550000000000002</v>
       </c>
       <c r="H18" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="I18" s="1">
         <v>5</v>
       </c>
-      <c r="I18" s="1">
-        <v>3.8</v>
-      </c>
       <c r="J18" s="5">
-        <f t="shared" si="1"/>
-        <v>1.7600000000000002</v>
+        <f>(AVERAGE(H18:I18)+N18)*0.4</f>
+        <v>2.3200000000000003</v>
       </c>
       <c r="K18" s="1">
-        <v>3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="L18" s="6">
-        <f t="shared" si="2"/>
-        <v>1.5</v>
-      </c>
-      <c r="M18" s="6"/>
+        <f>K18*0.5</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M18" s="6">
+        <v>9</v>
+      </c>
       <c r="N18" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>M18/10</f>
+        <v>0.9</v>
       </c>
       <c r="O18" s="6">
         <f>G18+J18+L18</f>
-        <v>3.524</v>
+        <v>3.8055000000000003</v>
       </c>
       <c r="P18" s="6">
         <f>INT(O18*10)/10+IF(MOD(O18*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q18" s="1" t="str">
         <f>IF(O18&lt;3,3-O18,"No aplica")</f>
@@ -5253,55 +5254,53 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="29">
-        <v>1087802193</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="31"/>
+      <c r="A19" s="19">
+        <v>1095551423</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="21"/>
       <c r="E19" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F19" s="1">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="0"/>
-        <v>0.22550000000000001</v>
+        <f>(E19*0.35+F19*0.65)*0.1</f>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H19" s="1">
         <v>5</v>
       </c>
       <c r="I19" s="1">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J19" s="5">
-        <f t="shared" si="1"/>
-        <v>2.3000000000000003</v>
+        <f>(AVERAGE(H19:I19)+N19)*0.4</f>
+        <v>1.7600000000000002</v>
       </c>
       <c r="K19" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L19" s="6">
-        <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="M19" s="6">
-        <v>9</v>
-      </c>
+        <f>K19*0.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="M19" s="6"/>
       <c r="N19" s="6">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
+        <f>M19/10</f>
+        <v>0</v>
       </c>
       <c r="O19" s="6">
         <f>G19+J19+L19</f>
-        <v>3.7755000000000001</v>
+        <v>3.524</v>
       </c>
       <c r="P19" s="6">
         <f>INT(O19*10)/10+IF(MOD(O19*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.8000000000000003</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" s="1" t="str">
         <f>IF(O19&lt;3,3-O19,"No aplica")</f>
@@ -5309,55 +5308,55 @@
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="29">
-        <v>1072747164</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="31"/>
+      <c r="A20" s="19">
+        <v>1087802193</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="21"/>
       <c r="E20" s="1">
         <v>0.5</v>
       </c>
       <c r="F20" s="1">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="0"/>
-        <v>0.28399999999999997</v>
+        <f>(E20*0.35+F20*0.65)*0.1</f>
+        <v>0.22550000000000001</v>
       </c>
       <c r="H20" s="1">
         <v>5</v>
       </c>
       <c r="I20" s="1">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J20" s="5">
-        <f t="shared" si="1"/>
-        <v>1.2800000000000002</v>
+        <f>(AVERAGE(H20:I20)+N20)*0.4</f>
+        <v>2.3000000000000003</v>
       </c>
       <c r="K20" s="1">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="L20" s="6">
-        <f t="shared" si="2"/>
-        <v>1.625</v>
+        <f>K20*0.5</f>
+        <v>1.25</v>
       </c>
       <c r="M20" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N20" s="6">
-        <f t="shared" si="3"/>
-        <v>0.7</v>
+        <f>M20/10</f>
+        <v>0.9</v>
       </c>
       <c r="O20" s="6">
         <f>G20+J20+L20</f>
-        <v>3.1890000000000001</v>
+        <v>3.7755000000000001</v>
       </c>
       <c r="P20" s="6">
         <f>INT(O20*10)/10+IF(MOD(O20*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.2</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="Q20" s="1" t="str">
         <f>IF(O20&lt;3,3-O20,"No aplica")</f>
@@ -5365,147 +5364,132 @@
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="29">
-        <v>1075234817</v>
-      </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="31"/>
+      <c r="A21" s="19">
+        <v>1072747164</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="21"/>
       <c r="E21" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E21*0.35+F21*0.65)*0.1</f>
+        <v>0.28399999999999997</v>
       </c>
       <c r="H21" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="1"/>
-        <v>1.92</v>
+        <f>(AVERAGE(H21:I21)+N21)*0.4</f>
+        <v>1.2800000000000002</v>
       </c>
       <c r="K21" s="1">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="L21" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9</v>
+        <f>K21*0.5</f>
+        <v>1.625</v>
       </c>
       <c r="M21" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N21" s="6">
-        <f t="shared" si="3"/>
-        <v>0.3</v>
+        <f>M21/10</f>
+        <v>0.7</v>
       </c>
       <c r="O21" s="6">
         <f>G21+J21+L21</f>
-        <v>2.82</v>
+        <v>3.1890000000000001</v>
       </c>
       <c r="P21" s="6">
         <f>INT(O21*10)/10+IF(MOD(O21*10,1)&gt;=0.5,0.1,0)</f>
-        <v>2.8</v>
-      </c>
-      <c r="Q21" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="Q21" s="1" t="str">
         <f>IF(O21&lt;3,3-O21,"No aplica")</f>
-        <v>0.18000000000000016</v>
+        <v>No aplica</v>
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="29">
-        <v>1016912717</v>
-      </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="31"/>
+      <c r="A22" s="19">
+        <v>1075234817</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="21"/>
       <c r="E22" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="0"/>
-        <v>0.10200000000000001</v>
+        <f>(E22*0.35+F22*0.65)*0.1</f>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1">
         <v>5</v>
       </c>
-      <c r="I22" s="1">
-        <v>4.5999999999999996</v>
-      </c>
       <c r="J22" s="5">
-        <f t="shared" si="1"/>
+        <f>(AVERAGE(H22:I22)+N22)*0.4</f>
         <v>1.92</v>
       </c>
       <c r="K22" s="1">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="2"/>
-        <v>1.875</v>
-      </c>
-      <c r="M22" s="6"/>
+        <f>K22*0.5</f>
+        <v>0.9</v>
+      </c>
+      <c r="M22" s="6">
+        <v>3</v>
+      </c>
       <c r="N22" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>M22/10</f>
+        <v>0.3</v>
       </c>
       <c r="O22" s="6">
         <f>G22+J22+L22</f>
-        <v>3.8969999999999998</v>
+        <v>2.82</v>
       </c>
       <c r="P22" s="6">
         <f>INT(O22*10)/10+IF(MOD(O22*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.9</v>
-      </c>
-      <c r="Q22" s="1" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="Q22" s="1">
         <f>IF(O22&lt;3,3-O22,"No aplica")</f>
-        <v>No aplica</v>
+        <v>0.18000000000000016</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A7:Q7" xr:uid="{7D02CB94-BE69-462D-965B-A4EABD13502C}">
+    <filterColumn colId="0" showButton="0"/>
+    <filterColumn colId="2" showButton="0"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:Q22">
+      <sortCondition ref="C7"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="43">
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:I3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="A6:D6"/>
@@ -5513,12 +5497,36 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <conditionalFormatting sqref="H8:I21">
     <cfRule type="expression" dxfId="11" priority="18">
